--- a/data/batches/2026-08/send_list.xlsx
+++ b/data/batches/2026-08/send_list.xlsx
@@ -925,454 +925,454 @@
     <t>Utami Wibowo</t>
   </si>
   <si>
-    <t>dimas.nasution608@outlook.com</t>
-  </si>
-  <si>
-    <t>vina.saputra573@gmail.com</t>
-  </si>
-  <si>
-    <t>tika.susanto926@gmail.com</t>
-  </si>
-  <si>
-    <t>nur.lestari650@gmail.com</t>
-  </si>
-  <si>
-    <t>joko.setiawan270@gmail.com</t>
-  </si>
-  <si>
-    <t>joko.nugroho688@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.siregar337@gmail.com</t>
-  </si>
-  <si>
-    <t>budi.siregar667@gmail.com</t>
-  </si>
-  <si>
-    <t>yuni.ramadhan958@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.setiawan655@outlook.com</t>
-  </si>
-  <si>
-    <t>budi.simanjuntak706@outlook.com</t>
-  </si>
-  <si>
-    <t>tika.firmansyah424@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.nugroho532@gmail.com</t>
-  </si>
-  <si>
-    <t>citra.siregar111@outlook.com</t>
-  </si>
-  <si>
-    <t>bayu.utomo296@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.permana689@gmail.com</t>
-  </si>
-  <si>
-    <t>laras.firmansyah350@outlook.com</t>
-  </si>
-  <si>
-    <t>kartika.halim174@outlook.com</t>
-  </si>
-  <si>
-    <t>kartika.nugroho952@gmail.com</t>
-  </si>
-  <si>
-    <t>wahyu.gunawan107@outlook.com</t>
-  </si>
-  <si>
-    <t>irfan.sitompul545@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>fitri.santoso810@outlook.com</t>
-  </si>
-  <si>
-    <t>surya.setiawan771@gmail.com</t>
-  </si>
-  <si>
-    <t>gilang.pratama510@outlook.com</t>
-  </si>
-  <si>
-    <t>surya.daeng364@outlook.com</t>
-  </si>
-  <si>
-    <t>andi.setiawan238.old@gmail.com</t>
-  </si>
-  <si>
-    <t>tika.marpaung805@outlook.com</t>
-  </si>
-  <si>
-    <t>mega.marpaung269@gmail.com</t>
-  </si>
-  <si>
-    <t>hendra.sitompul513@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>mega.firmansyah422@gmail.com</t>
-  </si>
-  <si>
-    <t>rizky.firmansyah364@gmail.com</t>
-  </si>
-  <si>
-    <t>joko.wijaya663@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.rahayu13@outlook.com</t>
-  </si>
-  <si>
-    <t>yoga.lestari340@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>yuni.saputra879@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>oki.hakim372@outlook.com</t>
-  </si>
-  <si>
-    <t>zaki.nasution210@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>rahmat.siregar757@gmail.com</t>
-  </si>
-  <si>
-    <t>gita.hidayat136@gmail.com</t>
-  </si>
-  <si>
-    <t>laras.ramadhan779@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>tika.wijaya764@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.harahap695@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.lestari789@gmail.com</t>
-  </si>
-  <si>
-    <t>gilang.daeng87@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.syahputra515@gmail.com</t>
-  </si>
-  <si>
-    <t>irfan.lestari524@gmail.com</t>
-  </si>
-  <si>
-    <t>rina.hakim486@gmail.com</t>
-  </si>
-  <si>
-    <t>utami.saputra534@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.firmansyah611@gmail.com</t>
-  </si>
-  <si>
-    <t>gilang.halim260@gmail.com</t>
-  </si>
-  <si>
-    <t>yuni.daeng514@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>eko.simanjuntak230@outlook.com</t>
-  </si>
-  <si>
-    <t>taufik.purnomo473@gmail.com</t>
-  </si>
-  <si>
-    <t>nur.kusuma124@gmail.com</t>
-  </si>
-  <si>
-    <t>bayu.setiawan607@gmail.com</t>
-  </si>
-  <si>
-    <t>bayu.gunawan728@outlook.com</t>
-  </si>
-  <si>
-    <t>zaki.purnomo501@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.nasution202@gmail.com</t>
-  </si>
-  <si>
-    <t>dewi.hidayat608@gmail.com</t>
-  </si>
-  <si>
-    <t>gita.nasution55@outlook.com</t>
-  </si>
-  <si>
-    <t>irfan.santoso944@gmail.com</t>
-  </si>
-  <si>
-    <t>indah.saputra104@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.kusuma887@outlook.com</t>
-  </si>
-  <si>
-    <t>eko.pane227@outlook.com</t>
-  </si>
-  <si>
-    <t>gilang.rahayu752@outlook.com</t>
-  </si>
-  <si>
-    <t>rina.nugroho236@gmail.com</t>
-  </si>
-  <si>
-    <t>citra.setiawan654@gmail.com</t>
-  </si>
-  <si>
-    <t>putri.firmansyah722@gmail.com</t>
-  </si>
-  <si>
-    <t>agus.nasution615@gmail.com</t>
-  </si>
-  <si>
-    <t>nur.santoso953@gmail.com</t>
-  </si>
-  <si>
-    <t>sari.lestari706@outlook.com</t>
-  </si>
-  <si>
-    <t>lestari.tanjung401@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.sitompul136@gmail.com</t>
-  </si>
-  <si>
-    <t>wahyu.purnomo929@gmail.com</t>
-  </si>
-  <si>
-    <t>oki.rahayu844@gmail.com</t>
-  </si>
-  <si>
-    <t>wulan.wijaya969@gmail.com</t>
-  </si>
-  <si>
-    <t>irfan.wijaya673@gmail.com</t>
-  </si>
-  <si>
-    <t>yoga.pane475@outlook.com</t>
-  </si>
-  <si>
-    <t>vina.purnomo192@outlook.com; indah.syahputra777@gmail.com</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak858@gmail.com</t>
-  </si>
-  <si>
-    <t>zaki.pane127@gmail.com</t>
-  </si>
-  <si>
-    <t>agus.halim86@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>agus.nugroho89@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>andi.purnomo234@gmail.com</t>
-  </si>
-  <si>
-    <t>joko.harahap511@gmail.com</t>
-  </si>
-  <si>
-    <t>nanda.marpaung438@gmail.com</t>
-  </si>
-  <si>
-    <t>irfan.tanjung184@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.utomo268@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.nasution871@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>maya.lestari694@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.wibowo163@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.rahayu969@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.pane811@gmail.com</t>
-  </si>
-  <si>
-    <t>nanda.pratama841@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>dimas.siregar658@gmail.com</t>
-  </si>
-  <si>
-    <t>fajar.purnomo953@gmail.com</t>
-  </si>
-  <si>
-    <t>agus.hakim526@gmial.com</t>
-  </si>
-  <si>
-    <t>putri.lestari568@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>joko.wibowo645@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>dewi.purnomo638@gmail.com</t>
-  </si>
-  <si>
-    <t>sari.wijaya789@outlook.com</t>
-  </si>
-  <si>
-    <t>bayu.hakim696@gmail.com</t>
-  </si>
-  <si>
-    <t>nanda.ramadhan287@outlook.com</t>
-  </si>
-  <si>
-    <t>bayu.harahap869@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>putri.sitompul57@gmail.com</t>
-  </si>
-  <si>
-    <t>irfan.gunawan138@gmail.com</t>
-  </si>
-  <si>
-    <t>wahyu.tanjung859@gmail.com</t>
-  </si>
-  <si>
-    <t>rizky.daeng504@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>mega.wibowo950@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>putri.rahayu941@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.nugroho227@gmail.com</t>
-  </si>
-  <si>
-    <t>joko.utomo267@outlook.com</t>
-  </si>
-  <si>
-    <t>joko.nasution268@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>laras.wibowo869@gmail.com</t>
-  </si>
-  <si>
-    <t>surya.santoso798@gmail.com</t>
-  </si>
-  <si>
-    <t>eko.pratama215@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.pratama107@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.pratama75@gmail.com</t>
-  </si>
-  <si>
-    <t>gita.harahap520@outlook.com</t>
-  </si>
-  <si>
-    <t>irfan.firmansyah131@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>budi.wibowo941@gmail.com</t>
-  </si>
-  <si>
-    <t>putri.tanjung36@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.sitompul890@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.nasution5@gmail.com</t>
-  </si>
-  <si>
-    <t>fitri.syahputra263@gmail.com</t>
-  </si>
-  <si>
-    <t>sari.nasution814@gmail.com</t>
-  </si>
-  <si>
-    <t>laras.simanjuntak14@outlook.com</t>
-  </si>
-  <si>
-    <t>surya.hidayat910@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.firmansyah974@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.ramadhan647@gmail.com</t>
-  </si>
-  <si>
-    <t>gilang.rahayu567@outlook.com</t>
-  </si>
-  <si>
-    <t>laras.nasution838@gmail.com</t>
-  </si>
-  <si>
-    <t>rahmat.hakim508@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>wahyu.marpaung230@outlook.com</t>
-  </si>
-  <si>
-    <t>gilang.purnomo421@gmail.com</t>
-  </si>
-  <si>
-    <t>dimas.susanto703@gmail.com</t>
-  </si>
-  <si>
-    <t>hana.nugroho214@outlook.com</t>
-  </si>
-  <si>
-    <t>lestari.tanjung978@outlook.com</t>
-  </si>
-  <si>
-    <t>joko.tanjung869@outlook.com</t>
-  </si>
-  <si>
-    <t>bayu.susanto849@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>gilang.wijaya476@gmail.com</t>
-  </si>
-  <si>
-    <t>vina.setiawan486@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>rina.utomo103@gmail.com</t>
-  </si>
-  <si>
-    <t>maya.permana531@gmail.com</t>
-  </si>
-  <si>
-    <t>utami.siregar3@gmail.com</t>
-  </si>
-  <si>
-    <t>lestari.daeng107@gmail.com</t>
-  </si>
-  <si>
-    <t>mega.utomo870@gmail.com</t>
-  </si>
-  <si>
-    <t>hana.utomo103@outlook.com</t>
-  </si>
-  <si>
-    <t>putri.purnomo589@yahoo.co.id</t>
-  </si>
-  <si>
-    <t>utami.wibowo65@yahoo.co.id</t>
+    <t>dimas.nasution608@outlook.example</t>
+  </si>
+  <si>
+    <t>vina.saputra573@gmail.example</t>
+  </si>
+  <si>
+    <t>tika.susanto926@gmail.example</t>
+  </si>
+  <si>
+    <t>nur.lestari650@gmail.example</t>
+  </si>
+  <si>
+    <t>joko.setiawan270@gmail.example</t>
+  </si>
+  <si>
+    <t>joko.nugroho688@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.siregar337@gmail.example</t>
+  </si>
+  <si>
+    <t>budi.siregar667@gmail.example</t>
+  </si>
+  <si>
+    <t>yuni.ramadhan958@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.setiawan655@outlook.example</t>
+  </si>
+  <si>
+    <t>budi.simanjuntak706@outlook.example</t>
+  </si>
+  <si>
+    <t>tika.firmansyah424@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.nugroho532@gmail.example</t>
+  </si>
+  <si>
+    <t>citra.siregar111@outlook.example</t>
+  </si>
+  <si>
+    <t>bayu.utomo296@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.permana689@gmail.example</t>
+  </si>
+  <si>
+    <t>laras.firmansyah350@outlook.example</t>
+  </si>
+  <si>
+    <t>kartika.halim174@outlook.example</t>
+  </si>
+  <si>
+    <t>kartika.nugroho952@gmail.example</t>
+  </si>
+  <si>
+    <t>wahyu.gunawan107@outlook.example</t>
+  </si>
+  <si>
+    <t>irfan.sitompul545@yahoo.example</t>
+  </si>
+  <si>
+    <t>fitri.santoso810@outlook.example</t>
+  </si>
+  <si>
+    <t>surya.setiawan771@gmail.example</t>
+  </si>
+  <si>
+    <t>gilang.pratama510@outlook.example</t>
+  </si>
+  <si>
+    <t>surya.daeng364@outlook.example</t>
+  </si>
+  <si>
+    <t>andi.setiawan238.old@gmail.example</t>
+  </si>
+  <si>
+    <t>tika.marpaung805@outlook.example</t>
+  </si>
+  <si>
+    <t>mega.marpaung269@gmail.example</t>
+  </si>
+  <si>
+    <t>hendra.sitompul513@yahoo.example</t>
+  </si>
+  <si>
+    <t>mega.firmansyah422@gmail.example</t>
+  </si>
+  <si>
+    <t>rizky.firmansyah364@gmail.example</t>
+  </si>
+  <si>
+    <t>joko.wijaya663@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.rahayu13@outlook.example</t>
+  </si>
+  <si>
+    <t>yoga.lestari340@yahoo.example</t>
+  </si>
+  <si>
+    <t>yuni.saputra879@yahoo.example</t>
+  </si>
+  <si>
+    <t>oki.hakim372@outlook.example</t>
+  </si>
+  <si>
+    <t>zaki.nasution210@yahoo.example</t>
+  </si>
+  <si>
+    <t>rahmat.siregar757@gmail.example</t>
+  </si>
+  <si>
+    <t>gita.hidayat136@gmail.example</t>
+  </si>
+  <si>
+    <t>laras.ramadhan779@yahoo.example</t>
+  </si>
+  <si>
+    <t>tika.wijaya764@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.harahap695@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.lestari789@gmail.example</t>
+  </si>
+  <si>
+    <t>gilang.daeng87@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.syahputra515@gmail.example</t>
+  </si>
+  <si>
+    <t>irfan.lestari524@gmail.example</t>
+  </si>
+  <si>
+    <t>rina.hakim486@gmail.example</t>
+  </si>
+  <si>
+    <t>utami.saputra534@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.firmansyah611@gmail.example</t>
+  </si>
+  <si>
+    <t>gilang.halim260@gmail.example</t>
+  </si>
+  <si>
+    <t>yuni.daeng514@yahoo.example</t>
+  </si>
+  <si>
+    <t>eko.simanjuntak230@outlook.example</t>
+  </si>
+  <si>
+    <t>taufik.purnomo473@gmail.example</t>
+  </si>
+  <si>
+    <t>nur.kusuma124@gmail.example</t>
+  </si>
+  <si>
+    <t>bayu.setiawan607@gmail.example</t>
+  </si>
+  <si>
+    <t>bayu.gunawan728@outlook.example</t>
+  </si>
+  <si>
+    <t>zaki.purnomo501@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.nasution202@gmail.example</t>
+  </si>
+  <si>
+    <t>dewi.hidayat608@gmail.example</t>
+  </si>
+  <si>
+    <t>gita.nasution55@outlook.example</t>
+  </si>
+  <si>
+    <t>irfan.santoso944@gmail.example</t>
+  </si>
+  <si>
+    <t>indah.saputra104@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.kusuma887@outlook.example</t>
+  </si>
+  <si>
+    <t>eko.pane227@outlook.example</t>
+  </si>
+  <si>
+    <t>gilang.rahayu752@outlook.example</t>
+  </si>
+  <si>
+    <t>rina.nugroho236@gmail.example</t>
+  </si>
+  <si>
+    <t>citra.setiawan654@gmail.example</t>
+  </si>
+  <si>
+    <t>putri.firmansyah722@gmail.example</t>
+  </si>
+  <si>
+    <t>agus.nasution615@gmail.example</t>
+  </si>
+  <si>
+    <t>nur.santoso953@gmail.example</t>
+  </si>
+  <si>
+    <t>sari.lestari706@outlook.example</t>
+  </si>
+  <si>
+    <t>lestari.tanjung401@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.sitompul136@gmail.example</t>
+  </si>
+  <si>
+    <t>wahyu.purnomo929@gmail.example</t>
+  </si>
+  <si>
+    <t>oki.rahayu844@gmail.example</t>
+  </si>
+  <si>
+    <t>wulan.wijaya969@gmail.example</t>
+  </si>
+  <si>
+    <t>irfan.wijaya673@gmail.example</t>
+  </si>
+  <si>
+    <t>yoga.pane475@outlook.example</t>
+  </si>
+  <si>
+    <t>vina.purnomo192@outlook.example; indah.syahputra777@gmail.example</t>
+  </si>
+  <si>
+    <t>dewi.simanjuntak858@gmail.example</t>
+  </si>
+  <si>
+    <t>zaki.pane127@gmail.example</t>
+  </si>
+  <si>
+    <t>agus.halim86@yahoo.example</t>
+  </si>
+  <si>
+    <t>agus.nugroho89@yahoo.example</t>
+  </si>
+  <si>
+    <t>andi.purnomo234@gmail.example</t>
+  </si>
+  <si>
+    <t>joko.harahap511@gmail.example</t>
+  </si>
+  <si>
+    <t>nanda.marpaung438@gmail.example</t>
+  </si>
+  <si>
+    <t>irfan.tanjung184@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.utomo268@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.nasution871@yahoo.example</t>
+  </si>
+  <si>
+    <t>maya.lestari694@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.wibowo163@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.rahayu969@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.pane811@gmail.example</t>
+  </si>
+  <si>
+    <t>nanda.pratama841@yahoo.example</t>
+  </si>
+  <si>
+    <t>dimas.siregar658@gmail.example</t>
+  </si>
+  <si>
+    <t>fajar.purnomo953@gmail.example</t>
+  </si>
+  <si>
+    <t>agus.hakim526@gmial.example</t>
+  </si>
+  <si>
+    <t>putri.lestari568@yahoo.example</t>
+  </si>
+  <si>
+    <t>joko.wibowo645@yahoo.example</t>
+  </si>
+  <si>
+    <t>dewi.purnomo638@gmail.example</t>
+  </si>
+  <si>
+    <t>sari.wijaya789@outlook.example</t>
+  </si>
+  <si>
+    <t>bayu.hakim696@gmail.example</t>
+  </si>
+  <si>
+    <t>nanda.ramadhan287@outlook.example</t>
+  </si>
+  <si>
+    <t>bayu.harahap869@yahoo.example</t>
+  </si>
+  <si>
+    <t>putri.sitompul57@gmail.example</t>
+  </si>
+  <si>
+    <t>irfan.gunawan138@gmail.example</t>
+  </si>
+  <si>
+    <t>wahyu.tanjung859@gmail.example</t>
+  </si>
+  <si>
+    <t>rizky.daeng504@yahoo.example</t>
+  </si>
+  <si>
+    <t>mega.wibowo950@yahoo.example</t>
+  </si>
+  <si>
+    <t>putri.rahayu941@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.nugroho227@gmail.example</t>
+  </si>
+  <si>
+    <t>joko.utomo267@outlook.example</t>
+  </si>
+  <si>
+    <t>joko.nasution268@yahoo.example</t>
+  </si>
+  <si>
+    <t>laras.wibowo869@gmail.example</t>
+  </si>
+  <si>
+    <t>surya.santoso798@gmail.example</t>
+  </si>
+  <si>
+    <t>eko.pratama215@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.pratama107@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.pratama75@gmail.example</t>
+  </si>
+  <si>
+    <t>gita.harahap520@outlook.example</t>
+  </si>
+  <si>
+    <t>irfan.firmansyah131@yahoo.example</t>
+  </si>
+  <si>
+    <t>budi.wibowo941@gmail.example</t>
+  </si>
+  <si>
+    <t>putri.tanjung36@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.sitompul890@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.nasution5@gmail.example</t>
+  </si>
+  <si>
+    <t>fitri.syahputra263@gmail.example</t>
+  </si>
+  <si>
+    <t>sari.nasution814@gmail.example</t>
+  </si>
+  <si>
+    <t>laras.simanjuntak14@outlook.example</t>
+  </si>
+  <si>
+    <t>surya.hidayat910@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.firmansyah974@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.ramadhan647@gmail.example</t>
+  </si>
+  <si>
+    <t>gilang.rahayu567@outlook.example</t>
+  </si>
+  <si>
+    <t>laras.nasution838@gmail.example</t>
+  </si>
+  <si>
+    <t>rahmat.hakim508@yahoo.example</t>
+  </si>
+  <si>
+    <t>wahyu.marpaung230@outlook.example</t>
+  </si>
+  <si>
+    <t>gilang.purnomo421@gmail.example</t>
+  </si>
+  <si>
+    <t>dimas.susanto703@gmail.example</t>
+  </si>
+  <si>
+    <t>hana.nugroho214@outlook.example</t>
+  </si>
+  <si>
+    <t>lestari.tanjung978@outlook.example</t>
+  </si>
+  <si>
+    <t>joko.tanjung869@outlook.example</t>
+  </si>
+  <si>
+    <t>bayu.susanto849@yahoo.example</t>
+  </si>
+  <si>
+    <t>gilang.wijaya476@gmail.example</t>
+  </si>
+  <si>
+    <t>vina.setiawan486@yahoo.example</t>
+  </si>
+  <si>
+    <t>rina.utomo103@gmail.example</t>
+  </si>
+  <si>
+    <t>maya.permana531@gmail.example</t>
+  </si>
+  <si>
+    <t>utami.siregar3@gmail.example</t>
+  </si>
+  <si>
+    <t>lestari.daeng107@gmail.example</t>
+  </si>
+  <si>
+    <t>mega.utomo870@gmail.example</t>
+  </si>
+  <si>
+    <t>hana.utomo103@outlook.example</t>
+  </si>
+  <si>
+    <t>putri.purnomo589@yahoo.example</t>
+  </si>
+  <si>
+    <t>utami.wibowo65@yahoo.example</t>
   </si>
   <si>
     <t>BDG</t>
@@ -1402,7 +1402,7 @@
     <t>MATURITY</t>
   </si>
   <si>
-    <t>mks.staff@gmail.com</t>
+    <t>mks.staff@gmail.example</t>
   </si>
 </sst>
 </file>

--- a/data/batches/2026-08/send_list.xlsx
+++ b/data/batches/2026-08/send_list.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="450">
   <si>
     <t>batch_id</t>
   </si>
@@ -40,1339 +40,1309 @@
     <t>2026-08</t>
   </si>
   <si>
-    <t>7746323254</t>
-  </si>
-  <si>
-    <t>7749781629</t>
-  </si>
-  <si>
-    <t>7709731924</t>
-  </si>
-  <si>
-    <t>7727134379</t>
-  </si>
-  <si>
-    <t>7797834056</t>
-  </si>
-  <si>
-    <t>7782312346</t>
-  </si>
-  <si>
-    <t>7794744011</t>
-  </si>
-  <si>
-    <t>7705768982</t>
-  </si>
-  <si>
-    <t>7782861690</t>
-  </si>
-  <si>
-    <t>7783297898</t>
-  </si>
-  <si>
-    <t>7783785272</t>
-  </si>
-  <si>
-    <t>7788176101</t>
-  </si>
-  <si>
-    <t>7758412590</t>
-  </si>
-  <si>
-    <t>7701662038</t>
-  </si>
-  <si>
-    <t>7782023749</t>
-  </si>
-  <si>
-    <t>7769072792</t>
-  </si>
-  <si>
-    <t>7751182194</t>
-  </si>
-  <si>
-    <t>7735030568</t>
-  </si>
-  <si>
-    <t>7755896168</t>
-  </si>
-  <si>
-    <t>7796268345</t>
-  </si>
-  <si>
-    <t>7739786224</t>
-  </si>
-  <si>
-    <t>7746284698</t>
-  </si>
-  <si>
-    <t>7724617701</t>
-  </si>
-  <si>
-    <t>7762444571</t>
-  </si>
-  <si>
-    <t>7723247100</t>
-  </si>
-  <si>
-    <t>7779425041</t>
-  </si>
-  <si>
-    <t>7745819152</t>
-  </si>
-  <si>
-    <t>7719786335</t>
-  </si>
-  <si>
-    <t>7729293288</t>
-  </si>
-  <si>
-    <t>7725970383</t>
-  </si>
-  <si>
-    <t>7761336114</t>
-  </si>
-  <si>
-    <t>7707782831</t>
-  </si>
-  <si>
-    <t>7786367442</t>
-  </si>
-  <si>
-    <t>7725803533</t>
-  </si>
-  <si>
-    <t>7718172856</t>
-  </si>
-  <si>
-    <t>7731165600</t>
-  </si>
-  <si>
-    <t>7762109156</t>
-  </si>
-  <si>
-    <t>7739002162</t>
-  </si>
-  <si>
-    <t>7734983146</t>
-  </si>
-  <si>
-    <t>7753973288</t>
-  </si>
-  <si>
-    <t>7732110252</t>
-  </si>
-  <si>
-    <t>7786944595</t>
-  </si>
-  <si>
-    <t>7726957655</t>
-  </si>
-  <si>
-    <t>7798674375</t>
-  </si>
-  <si>
-    <t>7798227701</t>
-  </si>
-  <si>
-    <t>7762123650</t>
-  </si>
-  <si>
-    <t>7704122147</t>
-  </si>
-  <si>
-    <t>7766929094</t>
-  </si>
-  <si>
-    <t>7750674988</t>
-  </si>
-  <si>
-    <t>7713356833</t>
-  </si>
-  <si>
-    <t>7777951818</t>
-  </si>
-  <si>
-    <t>7786214422</t>
-  </si>
-  <si>
-    <t>7763643347</t>
-  </si>
-  <si>
-    <t>7753176456</t>
-  </si>
-  <si>
-    <t>7768749581</t>
-  </si>
-  <si>
-    <t>7781871010</t>
-  </si>
-  <si>
-    <t>7700210634</t>
-  </si>
-  <si>
-    <t>7752659205</t>
-  </si>
-  <si>
-    <t>7748137785</t>
-  </si>
-  <si>
-    <t>7772100666</t>
-  </si>
-  <si>
-    <t>7755237092</t>
-  </si>
-  <si>
-    <t>7745671728</t>
-  </si>
-  <si>
-    <t>7783452746</t>
-  </si>
-  <si>
-    <t>7755160057</t>
-  </si>
-  <si>
-    <t>7756144614</t>
-  </si>
-  <si>
-    <t>7745203880</t>
-  </si>
-  <si>
-    <t>7797569860</t>
-  </si>
-  <si>
-    <t>7799314000</t>
-  </si>
-  <si>
-    <t>7709998048</t>
-  </si>
-  <si>
-    <t>7799810789</t>
-  </si>
-  <si>
-    <t>7774724656</t>
-  </si>
-  <si>
-    <t>7727267114</t>
-  </si>
-  <si>
-    <t>7753993392</t>
-  </si>
-  <si>
-    <t>7760743774</t>
-  </si>
-  <si>
-    <t>7712035814</t>
-  </si>
-  <si>
-    <t>7763546687</t>
-  </si>
-  <si>
-    <t>7716216070</t>
-  </si>
-  <si>
-    <t>7726252489</t>
-  </si>
-  <si>
-    <t>7749826421</t>
-  </si>
-  <si>
-    <t>7707449684</t>
-  </si>
-  <si>
-    <t>7722911781</t>
-  </si>
-  <si>
-    <t>7799043440</t>
-  </si>
-  <si>
-    <t>7773146277</t>
-  </si>
-  <si>
-    <t>7705609376</t>
-  </si>
-  <si>
-    <t>7715848084</t>
-  </si>
-  <si>
-    <t>7732055405</t>
-  </si>
-  <si>
-    <t>7722534988</t>
-  </si>
-  <si>
-    <t>7787831446</t>
-  </si>
-  <si>
-    <t>7723903624</t>
-  </si>
-  <si>
-    <t>7791247079</t>
-  </si>
-  <si>
-    <t>7701125657</t>
-  </si>
-  <si>
-    <t>7785667722</t>
-  </si>
-  <si>
-    <t>7754227136</t>
-  </si>
-  <si>
-    <t>7768739957</t>
-  </si>
-  <si>
-    <t>7788942088</t>
-  </si>
-  <si>
-    <t>7744923879</t>
-  </si>
-  <si>
-    <t>7702539622</t>
-  </si>
-  <si>
-    <t>7759675119</t>
-  </si>
-  <si>
-    <t>7749256988</t>
-  </si>
-  <si>
-    <t>7751956215</t>
-  </si>
-  <si>
-    <t>7718473738</t>
-  </si>
-  <si>
-    <t>7767887787</t>
-  </si>
-  <si>
-    <t>7774027335</t>
-  </si>
-  <si>
-    <t>7792282642</t>
-  </si>
-  <si>
-    <t>7767647122</t>
-  </si>
-  <si>
-    <t>7792098098</t>
-  </si>
-  <si>
-    <t>7797690923</t>
-  </si>
-  <si>
-    <t>7740791374</t>
-  </si>
-  <si>
-    <t>7753098843</t>
-  </si>
-  <si>
-    <t>7762754453</t>
+    <t>7791237918</t>
+  </si>
+  <si>
+    <t>7773036672</t>
+  </si>
+  <si>
+    <t>7784517408</t>
+  </si>
+  <si>
+    <t>7744765114</t>
+  </si>
+  <si>
+    <t>7785828392</t>
+  </si>
+  <si>
+    <t>7767425007</t>
+  </si>
+  <si>
+    <t>7781135007</t>
+  </si>
+  <si>
+    <t>7774819006</t>
+  </si>
+  <si>
+    <t>7749037636</t>
+  </si>
+  <si>
+    <t>7762350214</t>
+  </si>
+  <si>
+    <t>7784888121</t>
+  </si>
+  <si>
+    <t>7764889378</t>
+  </si>
+  <si>
+    <t>7793810852</t>
+  </si>
+  <si>
+    <t>7739161898</t>
+  </si>
+  <si>
+    <t>7748747227</t>
+  </si>
+  <si>
+    <t>7713314114</t>
+  </si>
+  <si>
+    <t>7787927537</t>
+  </si>
+  <si>
+    <t>7762808265</t>
+  </si>
+  <si>
+    <t>7704917079</t>
+  </si>
+  <si>
+    <t>7781335822</t>
+  </si>
+  <si>
+    <t>7716879932</t>
+  </si>
+  <si>
+    <t>7705357930</t>
+  </si>
+  <si>
+    <t>7788296150</t>
+  </si>
+  <si>
+    <t>7704707854</t>
+  </si>
+  <si>
+    <t>7746671249</t>
+  </si>
+  <si>
+    <t>7744558470</t>
+  </si>
+  <si>
+    <t>7703074997</t>
+  </si>
+  <si>
+    <t>7706761712</t>
+  </si>
+  <si>
+    <t>7757171487</t>
+  </si>
+  <si>
+    <t>7787171057</t>
+  </si>
+  <si>
+    <t>7720456047</t>
+  </si>
+  <si>
+    <t>7754915463</t>
+  </si>
+  <si>
+    <t>7724397078</t>
+  </si>
+  <si>
+    <t>7736193190</t>
+  </si>
+  <si>
+    <t>7709193255</t>
+  </si>
+  <si>
+    <t>7785769575</t>
+  </si>
+  <si>
+    <t>7760411767</t>
+  </si>
+  <si>
+    <t>7708722439</t>
+  </si>
+  <si>
+    <t>7751630334</t>
+  </si>
+  <si>
+    <t>7764063570</t>
+  </si>
+  <si>
+    <t>7786284849</t>
+  </si>
+  <si>
+    <t>7749464540</t>
+  </si>
+  <si>
+    <t>7764508726</t>
+  </si>
+  <si>
+    <t>7788035038</t>
+  </si>
+  <si>
+    <t>7707121345</t>
+  </si>
+  <si>
+    <t>7753651387</t>
+  </si>
+  <si>
+    <t>7713292035</t>
+  </si>
+  <si>
+    <t>7795724070</t>
+  </si>
+  <si>
+    <t>7710349388</t>
+  </si>
+  <si>
+    <t>7747657240</t>
+  </si>
+  <si>
+    <t>7719031847</t>
+  </si>
+  <si>
+    <t>7775513957</t>
+  </si>
+  <si>
+    <t>7771082356</t>
+  </si>
+  <si>
+    <t>7767907208</t>
+  </si>
+  <si>
+    <t>7720546494</t>
+  </si>
+  <si>
+    <t>7777166781</t>
+  </si>
+  <si>
+    <t>7719457637</t>
+  </si>
+  <si>
+    <t>7708477974</t>
+  </si>
+  <si>
+    <t>7751489974</t>
+  </si>
+  <si>
+    <t>7720852209</t>
+  </si>
+  <si>
+    <t>7710789322</t>
+  </si>
+  <si>
+    <t>7729917600</t>
+  </si>
+  <si>
+    <t>7741127086</t>
+  </si>
+  <si>
+    <t>7768576710</t>
+  </si>
+  <si>
+    <t>7795967214</t>
+  </si>
+  <si>
+    <t>7798844929</t>
+  </si>
+  <si>
+    <t>7776107565</t>
+  </si>
+  <si>
+    <t>7762652962</t>
+  </si>
+  <si>
+    <t>7740319965</t>
+  </si>
+  <si>
+    <t>7781124802</t>
+  </si>
+  <si>
+    <t>7709444919</t>
+  </si>
+  <si>
+    <t>7790610834</t>
+  </si>
+  <si>
+    <t>7707049462</t>
+  </si>
+  <si>
+    <t>7793838542</t>
+  </si>
+  <si>
+    <t>7731093920</t>
+  </si>
+  <si>
+    <t>7733303788</t>
+  </si>
+  <si>
+    <t>7770069870</t>
+  </si>
+  <si>
+    <t>7722802311</t>
+  </si>
+  <si>
+    <t>7720774229</t>
+  </si>
+  <si>
+    <t>7735393964</t>
+  </si>
+  <si>
+    <t>7719393962</t>
+  </si>
+  <si>
+    <t>7719775647</t>
+  </si>
+  <si>
+    <t>7799123141</t>
+  </si>
+  <si>
+    <t>7773965956</t>
+  </si>
+  <si>
+    <t>7791595487</t>
+  </si>
+  <si>
+    <t>7784406856</t>
+  </si>
+  <si>
+    <t>7746459181</t>
+  </si>
+  <si>
+    <t>7771997585</t>
+  </si>
+  <si>
+    <t>7788280043</t>
+  </si>
+  <si>
+    <t>7753203184</t>
+  </si>
+  <si>
+    <t>7792504463</t>
+  </si>
+  <si>
+    <t>7758916018</t>
+  </si>
+  <si>
+    <t>7755425450</t>
+  </si>
+  <si>
+    <t>7714745595</t>
+  </si>
+  <si>
+    <t>7731005775</t>
+  </si>
+  <si>
+    <t>7733682281</t>
+  </si>
+  <si>
+    <t>7739939699</t>
+  </si>
+  <si>
+    <t>7787369651</t>
+  </si>
+  <si>
+    <t>7710756537</t>
+  </si>
+  <si>
+    <t>7709655248</t>
+  </si>
+  <si>
+    <t>7739852985</t>
+  </si>
+  <si>
+    <t>7720149578</t>
+  </si>
+  <si>
+    <t>7786858017</t>
+  </si>
+  <si>
+    <t>7722280479</t>
+  </si>
+  <si>
+    <t>7717799490</t>
+  </si>
+  <si>
+    <t>7723340223</t>
+  </si>
+  <si>
+    <t>7715678162</t>
+  </si>
+  <si>
+    <t>7730016121</t>
+  </si>
+  <si>
+    <t>7703485488</t>
+  </si>
+  <si>
+    <t>7753716555</t>
+  </si>
+  <si>
+    <t>7791220776</t>
+  </si>
+  <si>
+    <t>7728339292</t>
+  </si>
+  <si>
+    <t>7731009808</t>
+  </si>
+  <si>
+    <t>7768298097</t>
+  </si>
+  <si>
+    <t>7702768399</t>
+  </si>
+  <si>
+    <t>7788591489</t>
+  </si>
+  <si>
+    <t>7778175903</t>
+  </si>
+  <si>
+    <t>7723882519</t>
+  </si>
+  <si>
+    <t>7780031486</t>
   </si>
   <si>
     <t>7708473078</t>
   </si>
   <si>
-    <t>7735920520</t>
-  </si>
-  <si>
-    <t>7731717287</t>
-  </si>
-  <si>
-    <t>7709842400</t>
-  </si>
-  <si>
-    <t>7701740024</t>
-  </si>
-  <si>
-    <t>7732613144</t>
-  </si>
-  <si>
-    <t>7760486169</t>
-  </si>
-  <si>
-    <t>7714975280</t>
-  </si>
-  <si>
-    <t>7721655992</t>
-  </si>
-  <si>
-    <t>7710763766</t>
-  </si>
-  <si>
-    <t>7735857128</t>
-  </si>
-  <si>
-    <t>7751164647</t>
-  </si>
-  <si>
-    <t>7704748404</t>
-  </si>
-  <si>
-    <t>7766488978</t>
-  </si>
-  <si>
-    <t>7795060988</t>
-  </si>
-  <si>
-    <t>7748432235</t>
-  </si>
-  <si>
-    <t>7787883143</t>
-  </si>
-  <si>
-    <t>7735443603</t>
-  </si>
-  <si>
-    <t>7781603453</t>
-  </si>
-  <si>
-    <t>7755975969</t>
-  </si>
-  <si>
-    <t>7706342956</t>
-  </si>
-  <si>
-    <t>7707652145</t>
-  </si>
-  <si>
-    <t>7780786665</t>
-  </si>
-  <si>
-    <t>7792954364</t>
-  </si>
-  <si>
-    <t>7766276407</t>
-  </si>
-  <si>
-    <t>7780613914</t>
-  </si>
-  <si>
-    <t>7791719686</t>
-  </si>
-  <si>
-    <t>7714128213</t>
-  </si>
-  <si>
-    <t>7708728827</t>
-  </si>
-  <si>
-    <t>7723062397</t>
-  </si>
-  <si>
-    <t>7736124739</t>
-  </si>
-  <si>
-    <t>7763303355</t>
-  </si>
-  <si>
-    <t>7785506317</t>
-  </si>
-  <si>
-    <t>7724424466</t>
-  </si>
-  <si>
-    <t>7760983566</t>
-  </si>
-  <si>
-    <t>7701243361</t>
-  </si>
-  <si>
-    <t>7796520203</t>
-  </si>
-  <si>
-    <t>7790348591</t>
-  </si>
-  <si>
-    <t>7732721408</t>
-  </si>
-  <si>
-    <t>7783350851</t>
-  </si>
-  <si>
-    <t>Dimas Nasution</t>
-  </si>
-  <si>
-    <t>Vina Saputra</t>
-  </si>
-  <si>
-    <t>Tika Susanto</t>
-  </si>
-  <si>
-    <t>Nur Lestari</t>
-  </si>
-  <si>
-    <t>Joko Setiawan</t>
-  </si>
-  <si>
-    <t>Joko Nugroho</t>
-  </si>
-  <si>
-    <t>Rahmat Siregar</t>
-  </si>
-  <si>
-    <t>Budi Siregar</t>
-  </si>
-  <si>
-    <t>Yuni Ramadhan</t>
-  </si>
-  <si>
-    <t>Vina Setiawan</t>
-  </si>
-  <si>
-    <t>Budi Simanjuntak</t>
-  </si>
-  <si>
-    <t>Tika Firmansyah</t>
-  </si>
-  <si>
-    <t>Lestari Nugroho</t>
-  </si>
-  <si>
-    <t>Citra Siregar</t>
-  </si>
-  <si>
-    <t>Bayu Utomo</t>
-  </si>
-  <si>
-    <t>Vina Permana</t>
-  </si>
-  <si>
-    <t>Laras Firmansyah</t>
-  </si>
-  <si>
-    <t>Kartika Halim</t>
-  </si>
-  <si>
-    <t>Kartika Nugroho</t>
-  </si>
-  <si>
-    <t>Wahyu Gunawan</t>
-  </si>
-  <si>
-    <t>Irfan Sitompul</t>
-  </si>
-  <si>
-    <t>Fitri Santoso</t>
-  </si>
-  <si>
-    <t>Surya Setiawan</t>
-  </si>
-  <si>
-    <t>Gilang Pratama</t>
-  </si>
-  <si>
-    <t>Surya Daeng</t>
-  </si>
-  <si>
-    <t>Andi Setiawan</t>
-  </si>
-  <si>
-    <t>Tika Marpaung</t>
-  </si>
-  <si>
-    <t>Mega Marpaung</t>
-  </si>
-  <si>
-    <t>Hendra Sitompul</t>
-  </si>
-  <si>
-    <t>Mega Firmansyah</t>
-  </si>
-  <si>
-    <t>Rizky Firmansyah</t>
-  </si>
-  <si>
-    <t>Joko Wijaya</t>
-  </si>
-  <si>
-    <t>Fitri Rahayu</t>
-  </si>
-  <si>
-    <t>Yoga Lestari</t>
-  </si>
-  <si>
-    <t>Yuni Saputra</t>
-  </si>
-  <si>
-    <t>Oki Hakim</t>
-  </si>
-  <si>
-    <t>Zaki Nasution</t>
-  </si>
-  <si>
-    <t>Gita Hidayat</t>
-  </si>
-  <si>
-    <t>Laras Ramadhan</t>
-  </si>
-  <si>
-    <t>Tika Wijaya</t>
-  </si>
-  <si>
-    <t>Vina Harahap</t>
-  </si>
-  <si>
-    <t>Lestari Lestari</t>
-  </si>
-  <si>
-    <t>Gilang Daeng</t>
-  </si>
-  <si>
-    <t>Mega Syahputra</t>
-  </si>
-  <si>
-    <t>Irfan Lestari</t>
-  </si>
-  <si>
-    <t>Rina Hakim</t>
-  </si>
-  <si>
-    <t>Utami Saputra</t>
-  </si>
-  <si>
-    <t>Eko Firmansyah</t>
-  </si>
-  <si>
-    <t>Gilang Halim</t>
-  </si>
-  <si>
-    <t>Yuni Daeng</t>
-  </si>
-  <si>
-    <t>Eko Simanjuntak</t>
-  </si>
-  <si>
-    <t>Taufik Purnomo</t>
-  </si>
-  <si>
-    <t>Nur Kusuma</t>
-  </si>
-  <si>
-    <t>Bayu Setiawan</t>
-  </si>
-  <si>
-    <t>Bayu Gunawan</t>
-  </si>
-  <si>
-    <t>Zaki Purnomo</t>
-  </si>
-  <si>
-    <t>Eko Nasution</t>
-  </si>
-  <si>
-    <t>Dewi Hidayat</t>
-  </si>
-  <si>
-    <t>Gita Nasution</t>
-  </si>
-  <si>
-    <t>Irfan Santoso</t>
-  </si>
-  <si>
-    <t>Indah Saputra</t>
-  </si>
-  <si>
-    <t>Eko Kusuma</t>
-  </si>
-  <si>
-    <t>Eko Pane</t>
-  </si>
-  <si>
-    <t>Gilang Rahayu</t>
-  </si>
-  <si>
-    <t>Rina Nugroho</t>
-  </si>
-  <si>
-    <t>Citra Setiawan</t>
-  </si>
-  <si>
-    <t>Putri Firmansyah</t>
-  </si>
-  <si>
-    <t>Agus Nasution</t>
-  </si>
-  <si>
-    <t>Nur Santoso</t>
-  </si>
-  <si>
-    <t>Sari Lestari</t>
-  </si>
-  <si>
-    <t>Lestari Tanjung</t>
-  </si>
-  <si>
-    <t>Fitri Sitompul</t>
-  </si>
-  <si>
-    <t>Wahyu Purnomo</t>
-  </si>
-  <si>
-    <t>Oki Rahayu</t>
-  </si>
-  <si>
-    <t>Wulan Wijaya</t>
-  </si>
-  <si>
-    <t>Irfan Wijaya</t>
-  </si>
-  <si>
-    <t>Yoga Pane</t>
-  </si>
-  <si>
-    <t>Vina Purnomo</t>
-  </si>
-  <si>
-    <t>Dewi Simanjuntak</t>
-  </si>
-  <si>
-    <t>Zaki Pane</t>
-  </si>
-  <si>
-    <t>Agus Halim</t>
-  </si>
-  <si>
-    <t>Agus Nugroho</t>
-  </si>
-  <si>
-    <t>Andi Purnomo</t>
-  </si>
-  <si>
-    <t>Joko Harahap</t>
-  </si>
-  <si>
-    <t>Nanda Marpaung</t>
-  </si>
-  <si>
-    <t>Irfan Tanjung</t>
-  </si>
-  <si>
-    <t>Fitri Utomo</t>
-  </si>
-  <si>
-    <t>Maya Lestari</t>
-  </si>
-  <si>
-    <t>Eko Wibowo</t>
-  </si>
-  <si>
-    <t>Mega Rahayu</t>
-  </si>
-  <si>
-    <t>Dimas Pane</t>
-  </si>
-  <si>
-    <t>Nanda Pratama</t>
-  </si>
-  <si>
-    <t>Dimas Siregar</t>
-  </si>
-  <si>
-    <t>Fajar Purnomo</t>
-  </si>
-  <si>
-    <t>Agus Hakim</t>
-  </si>
-  <si>
-    <t>Putri Lestari</t>
-  </si>
-  <si>
-    <t>Joko Wibowo</t>
-  </si>
-  <si>
-    <t>Dewi Purnomo</t>
-  </si>
-  <si>
-    <t>Sari Wijaya</t>
-  </si>
-  <si>
-    <t>Bayu Hakim</t>
-  </si>
-  <si>
-    <t>Nanda Ramadhan</t>
-  </si>
-  <si>
-    <t>Bayu Harahap</t>
-  </si>
-  <si>
-    <t>Putri Sitompul</t>
-  </si>
-  <si>
-    <t>Irfan Gunawan</t>
-  </si>
-  <si>
-    <t>Wahyu Tanjung</t>
-  </si>
-  <si>
-    <t>Rizky Daeng</t>
-  </si>
-  <si>
-    <t>Mega Wibowo</t>
-  </si>
-  <si>
-    <t>Putri Rahayu</t>
-  </si>
-  <si>
-    <t>Fitri Nugroho</t>
-  </si>
-  <si>
-    <t>Joko Utomo</t>
-  </si>
-  <si>
-    <t>Joko Nasution</t>
-  </si>
-  <si>
-    <t>Laras Wibowo</t>
-  </si>
-  <si>
-    <t>Surya Santoso</t>
-  </si>
-  <si>
-    <t>Eko Pratama</t>
-  </si>
-  <si>
-    <t>Lestari Pratama</t>
-  </si>
-  <si>
-    <t>Mega Pratama</t>
-  </si>
-  <si>
-    <t>Gita Harahap</t>
-  </si>
-  <si>
-    <t>Irfan Firmansyah</t>
-  </si>
-  <si>
-    <t>Budi Wibowo</t>
-  </si>
-  <si>
-    <t>Putri Tanjung</t>
-  </si>
-  <si>
-    <t>Dimas Sitompul</t>
-  </si>
-  <si>
-    <t>Mega Nasution</t>
-  </si>
-  <si>
-    <t>Fitri Syahputra</t>
-  </si>
-  <si>
-    <t>Sari Nasution</t>
-  </si>
-  <si>
-    <t>Laras Simanjuntak</t>
-  </si>
-  <si>
-    <t>Surya Hidayat</t>
-  </si>
-  <si>
-    <t>Rahmat Firmansyah</t>
-  </si>
-  <si>
-    <t>Dimas Ramadhan</t>
-  </si>
-  <si>
-    <t>Laras Nasution</t>
-  </si>
-  <si>
-    <t>Rahmat Hakim</t>
-  </si>
-  <si>
-    <t>Wahyu Marpaung</t>
-  </si>
-  <si>
-    <t>Gilang Purnomo</t>
-  </si>
-  <si>
-    <t>Dimas Susanto</t>
-  </si>
-  <si>
-    <t>Hana Nugroho</t>
-  </si>
-  <si>
-    <t>Joko Tanjung</t>
-  </si>
-  <si>
-    <t>Bayu Susanto</t>
-  </si>
-  <si>
-    <t>Gilang Wijaya</t>
-  </si>
-  <si>
-    <t>Rina Utomo</t>
-  </si>
-  <si>
-    <t>Maya Permana</t>
-  </si>
-  <si>
-    <t>Utami Siregar</t>
-  </si>
-  <si>
-    <t>Lestari Daeng</t>
-  </si>
-  <si>
-    <t>Mega Utomo</t>
-  </si>
-  <si>
-    <t>Hana Utomo</t>
-  </si>
-  <si>
-    <t>Putri Purnomo</t>
-  </si>
-  <si>
-    <t>Utami Wibowo</t>
-  </si>
-  <si>
-    <t>dimas.nasution608@outlook.example</t>
-  </si>
-  <si>
-    <t>vina.saputra573@gmail.example</t>
-  </si>
-  <si>
-    <t>tika.susanto926@gmail.example</t>
-  </si>
-  <si>
-    <t>nur.lestari650@gmail.example</t>
-  </si>
-  <si>
-    <t>joko.setiawan270@gmail.example</t>
-  </si>
-  <si>
-    <t>joko.nugroho688@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.siregar337@gmail.example</t>
-  </si>
-  <si>
-    <t>budi.siregar667@gmail.example</t>
-  </si>
-  <si>
-    <t>yuni.ramadhan958@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.setiawan655@outlook.example</t>
-  </si>
-  <si>
-    <t>budi.simanjuntak706@outlook.example</t>
-  </si>
-  <si>
-    <t>tika.firmansyah424@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.nugroho532@gmail.example</t>
-  </si>
-  <si>
-    <t>citra.siregar111@outlook.example</t>
-  </si>
-  <si>
-    <t>bayu.utomo296@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.permana689@gmail.example</t>
-  </si>
-  <si>
-    <t>laras.firmansyah350@outlook.example</t>
-  </si>
-  <si>
-    <t>kartika.halim174@outlook.example</t>
-  </si>
-  <si>
-    <t>kartika.nugroho952@gmail.example</t>
-  </si>
-  <si>
-    <t>wahyu.gunawan107@outlook.example</t>
-  </si>
-  <si>
-    <t>irfan.sitompul545@yahoo.example</t>
-  </si>
-  <si>
-    <t>fitri.santoso810@outlook.example</t>
-  </si>
-  <si>
-    <t>surya.setiawan771@gmail.example</t>
-  </si>
-  <si>
-    <t>gilang.pratama510@outlook.example</t>
-  </si>
-  <si>
-    <t>surya.daeng364@outlook.example</t>
-  </si>
-  <si>
-    <t>andi.setiawan238.old@gmail.example</t>
-  </si>
-  <si>
-    <t>tika.marpaung805@outlook.example</t>
-  </si>
-  <si>
-    <t>mega.marpaung269@gmail.example</t>
-  </si>
-  <si>
-    <t>hendra.sitompul513@yahoo.example</t>
-  </si>
-  <si>
-    <t>mega.firmansyah422@gmail.example</t>
-  </si>
-  <si>
-    <t>rizky.firmansyah364@gmail.example</t>
-  </si>
-  <si>
-    <t>joko.wijaya663@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.rahayu13@outlook.example</t>
-  </si>
-  <si>
-    <t>yoga.lestari340@yahoo.example</t>
-  </si>
-  <si>
-    <t>yuni.saputra879@yahoo.example</t>
-  </si>
-  <si>
-    <t>oki.hakim372@outlook.example</t>
-  </si>
-  <si>
-    <t>zaki.nasution210@yahoo.example</t>
-  </si>
-  <si>
-    <t>rahmat.siregar757@gmail.example</t>
-  </si>
-  <si>
-    <t>gita.hidayat136@gmail.example</t>
-  </si>
-  <si>
-    <t>laras.ramadhan779@yahoo.example</t>
-  </si>
-  <si>
-    <t>tika.wijaya764@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.harahap695@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.lestari789@gmail.example</t>
-  </si>
-  <si>
-    <t>gilang.daeng87@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.syahputra515@gmail.example</t>
-  </si>
-  <si>
-    <t>irfan.lestari524@gmail.example</t>
-  </si>
-  <si>
-    <t>rina.hakim486@gmail.example</t>
-  </si>
-  <si>
-    <t>utami.saputra534@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.firmansyah611@gmail.example</t>
-  </si>
-  <si>
-    <t>gilang.halim260@gmail.example</t>
-  </si>
-  <si>
-    <t>yuni.daeng514@yahoo.example</t>
-  </si>
-  <si>
-    <t>eko.simanjuntak230@outlook.example</t>
-  </si>
-  <si>
-    <t>taufik.purnomo473@gmail.example</t>
-  </si>
-  <si>
-    <t>nur.kusuma124@gmail.example</t>
-  </si>
-  <si>
-    <t>bayu.setiawan607@gmail.example</t>
-  </si>
-  <si>
-    <t>bayu.gunawan728@outlook.example</t>
-  </si>
-  <si>
-    <t>zaki.purnomo501@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.nasution202@gmail.example</t>
-  </si>
-  <si>
-    <t>dewi.hidayat608@gmail.example</t>
-  </si>
-  <si>
-    <t>gita.nasution55@outlook.example</t>
-  </si>
-  <si>
-    <t>irfan.santoso944@gmail.example</t>
-  </si>
-  <si>
-    <t>indah.saputra104@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.kusuma887@outlook.example</t>
-  </si>
-  <si>
-    <t>eko.pane227@outlook.example</t>
-  </si>
-  <si>
-    <t>gilang.rahayu752@outlook.example</t>
-  </si>
-  <si>
-    <t>rina.nugroho236@gmail.example</t>
-  </si>
-  <si>
-    <t>citra.setiawan654@gmail.example</t>
-  </si>
-  <si>
-    <t>putri.firmansyah722@gmail.example</t>
-  </si>
-  <si>
-    <t>agus.nasution615@gmail.example</t>
-  </si>
-  <si>
-    <t>nur.santoso953@gmail.example</t>
-  </si>
-  <si>
-    <t>sari.lestari706@outlook.example</t>
-  </si>
-  <si>
-    <t>lestari.tanjung401@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.sitompul136@gmail.example</t>
-  </si>
-  <si>
-    <t>wahyu.purnomo929@gmail.example</t>
-  </si>
-  <si>
-    <t>oki.rahayu844@gmail.example</t>
-  </si>
-  <si>
-    <t>wulan.wijaya969@gmail.example</t>
-  </si>
-  <si>
-    <t>irfan.wijaya673@gmail.example</t>
-  </si>
-  <si>
-    <t>yoga.pane475@outlook.example</t>
-  </si>
-  <si>
-    <t>vina.purnomo192@outlook.example; indah.syahputra777@gmail.example</t>
-  </si>
-  <si>
-    <t>dewi.simanjuntak858@gmail.example</t>
-  </si>
-  <si>
-    <t>zaki.pane127@gmail.example</t>
-  </si>
-  <si>
-    <t>agus.halim86@yahoo.example</t>
-  </si>
-  <si>
-    <t>agus.nugroho89@yahoo.example</t>
-  </si>
-  <si>
-    <t>andi.purnomo234@gmail.example</t>
-  </si>
-  <si>
-    <t>joko.harahap511@gmail.example</t>
-  </si>
-  <si>
-    <t>nanda.marpaung438@gmail.example</t>
-  </si>
-  <si>
-    <t>irfan.tanjung184@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.utomo268@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.nasution871@yahoo.example</t>
-  </si>
-  <si>
-    <t>maya.lestari694@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.wibowo163@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.rahayu969@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.pane811@gmail.example</t>
-  </si>
-  <si>
-    <t>nanda.pratama841@yahoo.example</t>
-  </si>
-  <si>
-    <t>dimas.siregar658@gmail.example</t>
-  </si>
-  <si>
-    <t>fajar.purnomo953@gmail.example</t>
-  </si>
-  <si>
-    <t>agus.hakim526@gmial.example</t>
-  </si>
-  <si>
-    <t>putri.lestari568@yahoo.example</t>
-  </si>
-  <si>
-    <t>joko.wibowo645@yahoo.example</t>
-  </si>
-  <si>
-    <t>dewi.purnomo638@gmail.example</t>
-  </si>
-  <si>
-    <t>sari.wijaya789@outlook.example</t>
-  </si>
-  <si>
-    <t>bayu.hakim696@gmail.example</t>
-  </si>
-  <si>
-    <t>nanda.ramadhan287@outlook.example</t>
-  </si>
-  <si>
-    <t>bayu.harahap869@yahoo.example</t>
-  </si>
-  <si>
-    <t>putri.sitompul57@gmail.example</t>
-  </si>
-  <si>
-    <t>irfan.gunawan138@gmail.example</t>
-  </si>
-  <si>
-    <t>wahyu.tanjung859@gmail.example</t>
-  </si>
-  <si>
-    <t>rizky.daeng504@yahoo.example</t>
-  </si>
-  <si>
-    <t>mega.wibowo950@yahoo.example</t>
-  </si>
-  <si>
-    <t>putri.rahayu941@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.nugroho227@gmail.example</t>
-  </si>
-  <si>
-    <t>joko.utomo267@outlook.example</t>
-  </si>
-  <si>
-    <t>joko.nasution268@yahoo.example</t>
-  </si>
-  <si>
-    <t>laras.wibowo869@gmail.example</t>
-  </si>
-  <si>
-    <t>surya.santoso798@gmail.example</t>
-  </si>
-  <si>
-    <t>eko.pratama215@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.pratama107@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.pratama75@gmail.example</t>
-  </si>
-  <si>
-    <t>gita.harahap520@outlook.example</t>
-  </si>
-  <si>
-    <t>irfan.firmansyah131@yahoo.example</t>
-  </si>
-  <si>
-    <t>budi.wibowo941@gmail.example</t>
-  </si>
-  <si>
-    <t>putri.tanjung36@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.sitompul890@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.nasution5@gmail.example</t>
-  </si>
-  <si>
-    <t>fitri.syahputra263@gmail.example</t>
-  </si>
-  <si>
-    <t>sari.nasution814@gmail.example</t>
-  </si>
-  <si>
-    <t>laras.simanjuntak14@outlook.example</t>
-  </si>
-  <si>
-    <t>surya.hidayat910@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.firmansyah974@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.ramadhan647@gmail.example</t>
-  </si>
-  <si>
-    <t>gilang.rahayu567@outlook.example</t>
-  </si>
-  <si>
-    <t>laras.nasution838@gmail.example</t>
-  </si>
-  <si>
-    <t>rahmat.hakim508@yahoo.example</t>
-  </si>
-  <si>
-    <t>wahyu.marpaung230@outlook.example</t>
-  </si>
-  <si>
-    <t>gilang.purnomo421@gmail.example</t>
-  </si>
-  <si>
-    <t>dimas.susanto703@gmail.example</t>
-  </si>
-  <si>
-    <t>hana.nugroho214@outlook.example</t>
-  </si>
-  <si>
-    <t>lestari.tanjung978@outlook.example</t>
-  </si>
-  <si>
-    <t>joko.tanjung869@outlook.example</t>
-  </si>
-  <si>
-    <t>bayu.susanto849@yahoo.example</t>
-  </si>
-  <si>
-    <t>gilang.wijaya476@gmail.example</t>
-  </si>
-  <si>
-    <t>vina.setiawan486@yahoo.example</t>
-  </si>
-  <si>
-    <t>rina.utomo103@gmail.example</t>
-  </si>
-  <si>
-    <t>maya.permana531@gmail.example</t>
-  </si>
-  <si>
-    <t>utami.siregar3@gmail.example</t>
-  </si>
-  <si>
-    <t>lestari.daeng107@gmail.example</t>
-  </si>
-  <si>
-    <t>mega.utomo870@gmail.example</t>
-  </si>
-  <si>
-    <t>hana.utomo103@outlook.example</t>
-  </si>
-  <si>
-    <t>putri.purnomo589@yahoo.example</t>
-  </si>
-  <si>
-    <t>utami.wibowo65@yahoo.example</t>
+    <t>7769661712</t>
+  </si>
+  <si>
+    <t>7778865078</t>
+  </si>
+  <si>
+    <t>7741867884</t>
+  </si>
+  <si>
+    <t>7785504636</t>
+  </si>
+  <si>
+    <t>7700030828</t>
+  </si>
+  <si>
+    <t>7718399272</t>
+  </si>
+  <si>
+    <t>7768657146</t>
+  </si>
+  <si>
+    <t>7764643598</t>
+  </si>
+  <si>
+    <t>7728526578</t>
+  </si>
+  <si>
+    <t>7790379502</t>
+  </si>
+  <si>
+    <t>7793154277</t>
+  </si>
+  <si>
+    <t>7715821537</t>
+  </si>
+  <si>
+    <t>7777655068</t>
+  </si>
+  <si>
+    <t>7791270638</t>
+  </si>
+  <si>
+    <t>7779269544</t>
+  </si>
+  <si>
+    <t>7792070437</t>
+  </si>
+  <si>
+    <t>7789442661</t>
+  </si>
+  <si>
+    <t>7799867712</t>
+  </si>
+  <si>
+    <t>7731275376</t>
+  </si>
+  <si>
+    <t>7756826099</t>
+  </si>
+  <si>
+    <t>7787913083</t>
+  </si>
+  <si>
+    <t>7724734202</t>
+  </si>
+  <si>
+    <t>7771382642</t>
+  </si>
+  <si>
+    <t>7746376321</t>
+  </si>
+  <si>
+    <t>7718481308</t>
+  </si>
+  <si>
+    <t>7767076787</t>
+  </si>
+  <si>
+    <t>7741709984</t>
+  </si>
+  <si>
+    <t>7720403813</t>
+  </si>
+  <si>
+    <t>7763560188</t>
+  </si>
+  <si>
+    <t>7703852550</t>
+  </si>
+  <si>
+    <t>Kartika N******</t>
+  </si>
+  <si>
+    <t>Yoga D****</t>
+  </si>
+  <si>
+    <t>Nanda W*****</t>
+  </si>
+  <si>
+    <t>Putri P******</t>
+  </si>
+  <si>
+    <t>Sari W*****</t>
+  </si>
+  <si>
+    <t>Yoga W*****</t>
+  </si>
+  <si>
+    <t>Mega H******</t>
+  </si>
+  <si>
+    <t>Hana G******</t>
+  </si>
+  <si>
+    <t>Tika D****</t>
+  </si>
+  <si>
+    <t>Gita L******</t>
+  </si>
+  <si>
+    <t>Budi F*********</t>
+  </si>
+  <si>
+    <t>Dewi P******</t>
+  </si>
+  <si>
+    <t>Nur H******</t>
+  </si>
+  <si>
+    <t>Dewi S******</t>
+  </si>
+  <si>
+    <t>Gita N*******</t>
+  </si>
+  <si>
+    <t>Bayu R*****</t>
+  </si>
+  <si>
+    <t>Agus T******</t>
+  </si>
+  <si>
+    <t>Agus M*******</t>
+  </si>
+  <si>
+    <t>Laras S******</t>
+  </si>
+  <si>
+    <t>Irfan F*********</t>
+  </si>
+  <si>
+    <t>Eko M*******</t>
+  </si>
+  <si>
+    <t>Wulan R*******</t>
+  </si>
+  <si>
+    <t>Dimas S*******</t>
+  </si>
+  <si>
+    <t>Eko U****</t>
+  </si>
+  <si>
+    <t>Kartika P******</t>
+  </si>
+  <si>
+    <t>Nur P******</t>
+  </si>
+  <si>
+    <t>Utami R*******</t>
+  </si>
+  <si>
+    <t>Budi H******</t>
+  </si>
+  <si>
+    <t>Sari P******</t>
+  </si>
+  <si>
+    <t>Vina P******</t>
+  </si>
+  <si>
+    <t>Utami S******</t>
+  </si>
+  <si>
+    <t>Eko S**********</t>
+  </si>
+  <si>
+    <t>Budi R*******</t>
+  </si>
+  <si>
+    <t>Nanda S******</t>
+  </si>
+  <si>
+    <t>Bayu K*****</t>
+  </si>
+  <si>
+    <t>Kartika L******</t>
+  </si>
+  <si>
+    <t>Dimas D****</t>
+  </si>
+  <si>
+    <t>Budi H****</t>
+  </si>
+  <si>
+    <t>Lestari D****</t>
+  </si>
+  <si>
+    <t>Kartika S******</t>
+  </si>
+  <si>
+    <t>Irfan H****</t>
+  </si>
+  <si>
+    <t>Laras W*****</t>
+  </si>
+  <si>
+    <t>Nur H****</t>
+  </si>
+  <si>
+    <t>Gilang N*******</t>
+  </si>
+  <si>
+    <t>Tika S**********</t>
+  </si>
+  <si>
+    <t>Indah W*****</t>
+  </si>
+  <si>
+    <t>Taufik P******</t>
+  </si>
+  <si>
+    <t>Gilang F*********</t>
+  </si>
+  <si>
+    <t>Joko N******</t>
+  </si>
+  <si>
+    <t>Yuni S**********</t>
+  </si>
+  <si>
+    <t>Eko G******</t>
+  </si>
+  <si>
+    <t>Gita K*****</t>
+  </si>
+  <si>
+    <t>Irfan P******</t>
+  </si>
+  <si>
+    <t>Yuni F*********</t>
+  </si>
+  <si>
+    <t>Yuni P******</t>
+  </si>
+  <si>
+    <t>Mega R*****</t>
+  </si>
+  <si>
+    <t>Hana P******</t>
+  </si>
+  <si>
+    <t>Gilang R*****</t>
+  </si>
+  <si>
+    <t>Nanda T******</t>
+  </si>
+  <si>
+    <t>Kartika S*******</t>
+  </si>
+  <si>
+    <t>Taufik U****</t>
+  </si>
+  <si>
+    <t>Utami K*****</t>
+  </si>
+  <si>
+    <t>Hendra H******</t>
+  </si>
+  <si>
+    <t>Rizky S******</t>
+  </si>
+  <si>
+    <t>Dimas U****</t>
+  </si>
+  <si>
+    <t>Gita S******</t>
+  </si>
+  <si>
+    <t>Rina W*****</t>
+  </si>
+  <si>
+    <t>Rina M*******</t>
+  </si>
+  <si>
+    <t>Kartika H******</t>
+  </si>
+  <si>
+    <t>Dewi M*******</t>
+  </si>
+  <si>
+    <t>Wulan F*********</t>
+  </si>
+  <si>
+    <t>Fajar S**********</t>
+  </si>
+  <si>
+    <t>Nur K*****</t>
+  </si>
+  <si>
+    <t>Indah S******</t>
+  </si>
+  <si>
+    <t>Indah N******</t>
+  </si>
+  <si>
+    <t>Mega S**********</t>
+  </si>
+  <si>
+    <t>Hana S******</t>
+  </si>
+  <si>
+    <t>Taufik G******</t>
+  </si>
+  <si>
+    <t>Fitri S**********</t>
+  </si>
+  <si>
+    <t>Hana W*****</t>
+  </si>
+  <si>
+    <t>Yoga S******</t>
+  </si>
+  <si>
+    <t>Kartika R*******</t>
+  </si>
+  <si>
+    <t>Bayu D****</t>
+  </si>
+  <si>
+    <t>Agus L******</t>
+  </si>
+  <si>
+    <t>Dewi N******</t>
+  </si>
+  <si>
+    <t>Fitri P******</t>
+  </si>
+  <si>
+    <t>Indah P******</t>
+  </si>
+  <si>
+    <t>Zaki S*******</t>
+  </si>
+  <si>
+    <t>Yoga R*****</t>
+  </si>
+  <si>
+    <t>Agus D****</t>
+  </si>
+  <si>
+    <t>Tika F*********</t>
+  </si>
+  <si>
+    <t>Bayu S******</t>
+  </si>
+  <si>
+    <t>Gita S*******</t>
+  </si>
+  <si>
+    <t>Utami S*******</t>
+  </si>
+  <si>
+    <t>Taufik H****</t>
+  </si>
+  <si>
+    <t>Agus G******</t>
+  </si>
+  <si>
+    <t>Andi R*****</t>
+  </si>
+  <si>
+    <t>Putri S********</t>
+  </si>
+  <si>
+    <t>Taufik N******</t>
+  </si>
+  <si>
+    <t>Bayu P******</t>
+  </si>
+  <si>
+    <t>Wahyu S******</t>
+  </si>
+  <si>
+    <t>Joko S******</t>
+  </si>
+  <si>
+    <t>Zaki H******</t>
+  </si>
+  <si>
+    <t>Oki H******</t>
+  </si>
+  <si>
+    <t>Nanda F*********</t>
+  </si>
+  <si>
+    <t>Laras H******</t>
+  </si>
+  <si>
+    <t>Tika H****</t>
+  </si>
+  <si>
+    <t>Fitri N******</t>
+  </si>
+  <si>
+    <t>Dewi D****</t>
+  </si>
+  <si>
+    <t>Budi S*******</t>
+  </si>
+  <si>
+    <t>Zaki S******</t>
+  </si>
+  <si>
+    <t>Agus S******</t>
+  </si>
+  <si>
+    <t>Sari M*******</t>
+  </si>
+  <si>
+    <t>Eko S********</t>
+  </si>
+  <si>
+    <t>Dewi S********</t>
+  </si>
+  <si>
+    <t>Andi G******</t>
+  </si>
+  <si>
+    <t>Putri S******</t>
+  </si>
+  <si>
+    <t>Hana L******</t>
+  </si>
+  <si>
+    <t>Vina P***</t>
+  </si>
+  <si>
+    <t>Hana R*******</t>
+  </si>
+  <si>
+    <t>Rina S******</t>
+  </si>
+  <si>
+    <t>Nur S******</t>
+  </si>
+  <si>
+    <t>Andi N******</t>
+  </si>
+  <si>
+    <t>Eko P******</t>
+  </si>
+  <si>
+    <t>Hendra P******</t>
+  </si>
+  <si>
+    <t>Wahyu H****</t>
+  </si>
+  <si>
+    <t>Surya W*****</t>
+  </si>
+  <si>
+    <t>Fitri G******</t>
+  </si>
+  <si>
+    <t>Citra L******</t>
+  </si>
+  <si>
+    <t>Surya P******</t>
+  </si>
+  <si>
+    <t>Tika S*******</t>
+  </si>
+  <si>
+    <t>Nur N******</t>
+  </si>
+  <si>
+    <t>customer.0323@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0684@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0334@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0741@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0330@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0748@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0522@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0397@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0836@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0082@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0556@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0810@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0388@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0784@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0634@gmial.example</t>
+  </si>
+  <si>
+    <t>customer.0335@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0086@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0486@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0552@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0421@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0455@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0059@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0582@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0469@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0853@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0103@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0147@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0002@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0644@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0265@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0553@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0839@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0554@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0829@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0653@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0730@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0315@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0767@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0020@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0341@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0175@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0755@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0524@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0276@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0279@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0812@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0396@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0179@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0840@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0074@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0105@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0435@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0003@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0113@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0245@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0143@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0150@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0465@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0232@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0774@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0199@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0646@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0876@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0024@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0670@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0379@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0352@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0866@yahoo.example; customer.0233@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0809@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0261@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0783@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0673@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0550@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0291@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0418@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0649@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0458@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0470@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0092@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0066@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0707@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0040@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0358@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0766@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0717@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0820@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0188@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0857@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0240@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0728@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0523.old@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0406@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0787@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0593@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0091@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0137@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0657@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0297@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0689@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0540@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0011@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0759@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0743@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0475@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0872@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0157@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0622@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0141@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0662@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0182@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0277@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0445@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0145@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0233@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0503@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0867@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0507@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0723@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0267@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0449@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0690@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0269@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0078@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0052@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0196@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0621@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0427@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0500.old@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0616@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0252@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0248@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0451@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0570@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0019@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0752@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0765@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0333@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0770@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0579@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0262@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0351@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0769@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0006@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0818@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0102@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0601@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0489@gmail.example</t>
+  </si>
+  <si>
+    <t>customer.0439@outlook.example</t>
+  </si>
+  <si>
+    <t>customer.0046@yahoo.example</t>
+  </si>
+  <si>
+    <t>customer.0213@yahoo.example</t>
+  </si>
+  <si>
+    <t>JKT</t>
+  </si>
+  <si>
+    <t>YGY</t>
+  </si>
+  <si>
+    <t>MDN</t>
   </si>
   <si>
     <t>BDG</t>
@@ -1381,28 +1351,19 @@
     <t>SBY</t>
   </si>
   <si>
-    <t>MDN</t>
-  </si>
-  <si>
-    <t>JKT</t>
-  </si>
-  <si>
     <t>MKS</t>
   </si>
   <si>
-    <t>YGY</t>
+    <t>MATURITY</t>
+  </si>
+  <si>
+    <t>REINSTATEMENT</t>
   </si>
   <si>
     <t>BENEFIT_PAYMENT</t>
   </si>
   <si>
-    <t>REINSTATEMENT</t>
-  </si>
-  <si>
-    <t>MATURITY</t>
-  </si>
-  <si>
-    <t>mks.staff@gmail.example</t>
+    <t>ygy.staff@gmail.example</t>
   </si>
 </sst>
 </file>
@@ -1771,13 +1732,13 @@
         <v>158</v>
       </c>
       <c r="D2" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="F2" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1791,13 +1752,13 @@
         <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="E3" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F3" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -1811,13 +1772,13 @@
         <v>160</v>
       </c>
       <c r="D4" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="E4" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F4" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -1831,13 +1792,13 @@
         <v>161</v>
       </c>
       <c r="D5" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="E5" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F5" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -1851,13 +1812,13 @@
         <v>162</v>
       </c>
       <c r="D6" t="s">
-        <v>307</v>
+        <v>294</v>
       </c>
       <c r="E6" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F6" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -1871,13 +1832,13 @@
         <v>163</v>
       </c>
       <c r="D7" t="s">
-        <v>308</v>
+        <v>295</v>
       </c>
       <c r="E7" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="F7" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -1891,13 +1852,13 @@
         <v>164</v>
       </c>
       <c r="D8" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="E8" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F8" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -1911,13 +1872,13 @@
         <v>165</v>
       </c>
       <c r="D9" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="E9" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F9" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -1931,13 +1892,13 @@
         <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="E10" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F10" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -1951,13 +1912,13 @@
         <v>167</v>
       </c>
       <c r="D11" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="E11" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F11" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -1971,13 +1932,13 @@
         <v>168</v>
       </c>
       <c r="D12" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="E12" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F12" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -1991,13 +1952,13 @@
         <v>169</v>
       </c>
       <c r="D13" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="E13" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="F13" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2011,13 +1972,13 @@
         <v>170</v>
       </c>
       <c r="D14" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="E14" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="F14" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -2031,13 +1992,13 @@
         <v>171</v>
       </c>
       <c r="D15" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="E15" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F15" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -2051,13 +2012,13 @@
         <v>172</v>
       </c>
       <c r="D16" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="E16" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F16" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -2071,13 +2032,13 @@
         <v>173</v>
       </c>
       <c r="D17" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="E17" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="F17" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -2091,13 +2052,13 @@
         <v>174</v>
       </c>
       <c r="D18" t="s">
-        <v>319</v>
+        <v>306</v>
       </c>
       <c r="E18" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F18" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -2111,13 +2072,13 @@
         <v>175</v>
       </c>
       <c r="D19" t="s">
-        <v>320</v>
+        <v>307</v>
       </c>
       <c r="E19" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="F19" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -2131,13 +2092,13 @@
         <v>176</v>
       </c>
       <c r="D20" t="s">
-        <v>321</v>
+        <v>308</v>
       </c>
       <c r="E20" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="F20" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -2151,13 +2112,13 @@
         <v>177</v>
       </c>
       <c r="D21" t="s">
-        <v>322</v>
+        <v>309</v>
       </c>
       <c r="E21" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F21" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -2171,13 +2132,13 @@
         <v>178</v>
       </c>
       <c r="D22" t="s">
-        <v>323</v>
+        <v>310</v>
       </c>
       <c r="E22" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F22" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -2191,13 +2152,13 @@
         <v>179</v>
       </c>
       <c r="D23" t="s">
-        <v>324</v>
+        <v>311</v>
       </c>
       <c r="E23" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="F23" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -2211,13 +2172,13 @@
         <v>180</v>
       </c>
       <c r="D24" t="s">
-        <v>325</v>
+        <v>312</v>
       </c>
       <c r="E24" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F24" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -2231,13 +2192,13 @@
         <v>181</v>
       </c>
       <c r="D25" t="s">
-        <v>326</v>
+        <v>313</v>
       </c>
       <c r="E25" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F25" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -2251,13 +2212,13 @@
         <v>182</v>
       </c>
       <c r="D26" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="E26" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="F26" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2271,13 +2232,13 @@
         <v>183</v>
       </c>
       <c r="D27" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="E27" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="F27" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -2291,13 +2252,13 @@
         <v>184</v>
       </c>
       <c r="D28" t="s">
-        <v>329</v>
+        <v>316</v>
       </c>
       <c r="E28" t="s">
-        <v>457</v>
+        <v>443</v>
       </c>
       <c r="F28" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="29" spans="1:6">
@@ -2311,13 +2272,13 @@
         <v>185</v>
       </c>
       <c r="D29" t="s">
-        <v>330</v>
+        <v>317</v>
       </c>
       <c r="E29" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="F29" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -2331,13 +2292,13 @@
         <v>186</v>
       </c>
       <c r="D30" t="s">
-        <v>331</v>
+        <v>318</v>
       </c>
       <c r="E30" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="F30" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -2351,13 +2312,13 @@
         <v>187</v>
       </c>
       <c r="D31" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="E31" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="F31" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -2371,16 +2332,16 @@
         <v>188</v>
       </c>
       <c r="D32" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="E32" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F32" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33" t="s">
         <v>7</v>
       </c>
@@ -2391,16 +2352,16 @@
         <v>189</v>
       </c>
       <c r="D33" t="s">
-        <v>334</v>
+        <v>321</v>
       </c>
       <c r="E33" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="F33" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34" t="s">
         <v>7</v>
       </c>
@@ -2411,16 +2372,16 @@
         <v>190</v>
       </c>
       <c r="D34" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="E34" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F34" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35" t="s">
         <v>7</v>
       </c>
@@ -2431,16 +2392,16 @@
         <v>191</v>
       </c>
       <c r="D35" t="s">
-        <v>336</v>
+        <v>323</v>
       </c>
       <c r="E35" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="F35" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36" t="s">
         <v>7</v>
       </c>
@@ -2451,16 +2412,16 @@
         <v>192</v>
       </c>
       <c r="D36" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="E36" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F36" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37" t="s">
         <v>7</v>
       </c>
@@ -2471,16 +2432,16 @@
         <v>193</v>
       </c>
       <c r="D37" t="s">
-        <v>338</v>
+        <v>325</v>
       </c>
       <c r="E37" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="F37" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38" t="s">
         <v>7</v>
       </c>
@@ -2488,19 +2449,19 @@
         <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>194</v>
+        <v>161</v>
       </c>
       <c r="D38" t="s">
-        <v>339</v>
+        <v>326</v>
       </c>
       <c r="E38" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="F38" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39" t="s">
         <v>7</v>
       </c>
@@ -2508,19 +2469,19 @@
         <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>164</v>
+        <v>194</v>
       </c>
       <c r="D39" t="s">
-        <v>340</v>
+        <v>327</v>
       </c>
       <c r="E39" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="F39" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40" t="s">
         <v>7</v>
       </c>
@@ -2531,16 +2492,16 @@
         <v>195</v>
       </c>
       <c r="D40" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="E40" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="F40" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41" t="s">
         <v>7</v>
       </c>
@@ -2551,16 +2512,16 @@
         <v>196</v>
       </c>
       <c r="D41" t="s">
-        <v>342</v>
+        <v>329</v>
       </c>
       <c r="E41" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="F41" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42" t="s">
         <v>7</v>
       </c>
@@ -2571,16 +2532,16 @@
         <v>197</v>
       </c>
       <c r="D42" t="s">
-        <v>343</v>
+        <v>330</v>
       </c>
       <c r="E42" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F42" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43" t="s">
         <v>7</v>
       </c>
@@ -2591,16 +2552,16 @@
         <v>198</v>
       </c>
       <c r="D43" t="s">
-        <v>344</v>
+        <v>331</v>
       </c>
       <c r="E43" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F43" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44" t="s">
         <v>7</v>
       </c>
@@ -2611,16 +2572,16 @@
         <v>199</v>
       </c>
       <c r="D44" t="s">
-        <v>345</v>
+        <v>332</v>
       </c>
       <c r="E44" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="F44" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
       <c r="A45" t="s">
         <v>7</v>
       </c>
@@ -2631,16 +2592,19 @@
         <v>200</v>
       </c>
       <c r="D45" t="s">
-        <v>346</v>
+        <v>333</v>
       </c>
       <c r="E45" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F45" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>446</v>
+      </c>
+      <c r="G45" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
       <c r="A46" t="s">
         <v>7</v>
       </c>
@@ -2651,16 +2615,16 @@
         <v>201</v>
       </c>
       <c r="D46" t="s">
-        <v>347</v>
+        <v>334</v>
       </c>
       <c r="E46" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F46" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
       <c r="A47" t="s">
         <v>7</v>
       </c>
@@ -2671,16 +2635,16 @@
         <v>202</v>
       </c>
       <c r="D47" t="s">
-        <v>348</v>
+        <v>335</v>
       </c>
       <c r="E47" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="F47" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
       <c r="A48" t="s">
         <v>7</v>
       </c>
@@ -2691,13 +2655,13 @@
         <v>203</v>
       </c>
       <c r="D48" t="s">
-        <v>349</v>
+        <v>336</v>
       </c>
       <c r="E48" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="F48" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -2711,13 +2675,13 @@
         <v>204</v>
       </c>
       <c r="D49" t="s">
-        <v>350</v>
+        <v>337</v>
       </c>
       <c r="E49" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F49" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -2728,16 +2692,16 @@
         <v>56</v>
       </c>
       <c r="C50" t="s">
-        <v>205</v>
+        <v>171</v>
       </c>
       <c r="D50" t="s">
-        <v>351</v>
+        <v>338</v>
       </c>
       <c r="E50" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F50" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -2748,16 +2712,16 @@
         <v>57</v>
       </c>
       <c r="C51" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D51" t="s">
-        <v>352</v>
+        <v>339</v>
       </c>
       <c r="E51" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F51" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -2768,16 +2732,16 @@
         <v>58</v>
       </c>
       <c r="C52" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D52" t="s">
-        <v>353</v>
+        <v>340</v>
       </c>
       <c r="E52" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F52" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -2788,16 +2752,16 @@
         <v>59</v>
       </c>
       <c r="C53" t="s">
-        <v>208</v>
+        <v>173</v>
       </c>
       <c r="D53" t="s">
-        <v>354</v>
+        <v>341</v>
       </c>
       <c r="E53" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F53" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -2808,16 +2772,16 @@
         <v>60</v>
       </c>
       <c r="C54" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="D54" t="s">
-        <v>355</v>
+        <v>342</v>
       </c>
       <c r="E54" t="s">
-        <v>456</v>
+        <v>442</v>
       </c>
       <c r="F54" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="55" spans="1:6">
@@ -2828,16 +2792,16 @@
         <v>61</v>
       </c>
       <c r="C55" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="D55" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="E55" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="F55" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="56" spans="1:6">
@@ -2848,16 +2812,16 @@
         <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="D56" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="E56" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F56" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="57" spans="1:6">
@@ -2868,16 +2832,16 @@
         <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D57" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="E57" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="F57" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="58" spans="1:6">
@@ -2888,16 +2852,16 @@
         <v>64</v>
       </c>
       <c r="C58" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="D58" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="E58" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="F58" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="59" spans="1:6">
@@ -2908,16 +2872,16 @@
         <v>65</v>
       </c>
       <c r="C59" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D59" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="E59" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="F59" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="60" spans="1:6">
@@ -2928,16 +2892,16 @@
         <v>66</v>
       </c>
       <c r="C60" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D60" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="E60" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F60" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="61" spans="1:6">
@@ -2948,16 +2912,16 @@
         <v>67</v>
       </c>
       <c r="C61" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D61" t="s">
-        <v>362</v>
+        <v>349</v>
       </c>
       <c r="E61" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F61" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="62" spans="1:6">
@@ -2968,16 +2932,16 @@
         <v>68</v>
       </c>
       <c r="C62" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D62" t="s">
-        <v>363</v>
+        <v>350</v>
       </c>
       <c r="E62" t="s">
-        <v>453</v>
+        <v>441</v>
       </c>
       <c r="F62" t="s">
-        <v>461</v>
+        <v>447</v>
       </c>
     </row>
     <row r="63" spans="1:6">
@@ -2988,16 +2952,16 @@
         <v>69</v>
       </c>
       <c r="C63" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D63" t="s">
-        <v>364</v>
+        <v>351</v>
       </c>
       <c r="E63" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F63" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="64" spans="1:6">
@@ -3008,16 +2972,16 @@
         <v>70</v>
       </c>
       <c r="C64" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D64" t="s">
-        <v>365</v>
+        <v>352</v>
       </c>
       <c r="E64" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="F64" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="65" spans="1:6">
@@ -3028,16 +2992,16 @@
         <v>71</v>
       </c>
       <c r="C65" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D65" t="s">
-        <v>366</v>
+        <v>353</v>
       </c>
       <c r="E65" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="F65" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="66" spans="1:6">
@@ -3048,16 +3012,16 @@
         <v>72</v>
       </c>
       <c r="C66" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="D66" t="s">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="E66" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="F66" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="67" spans="1:6">
@@ -3068,16 +3032,16 @@
         <v>73</v>
       </c>
       <c r="C67" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="D67" t="s">
-        <v>368</v>
+        <v>355</v>
       </c>
       <c r="E67" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F67" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="68" spans="1:6">
@@ -3088,16 +3052,16 @@
         <v>74</v>
       </c>
       <c r="C68" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D68" t="s">
-        <v>369</v>
+        <v>356</v>
       </c>
       <c r="E68" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="F68" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="69" spans="1:6">
@@ -3108,16 +3072,16 @@
         <v>75</v>
       </c>
       <c r="C69" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D69" t="s">
-        <v>370</v>
+        <v>357</v>
       </c>
       <c r="E69" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="F69" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="70" spans="1:6">
@@ -3128,16 +3092,16 @@
         <v>76</v>
       </c>
       <c r="C70" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D70" t="s">
-        <v>371</v>
+        <v>358</v>
       </c>
       <c r="E70" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="F70" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="71" spans="1:6">
@@ -3148,16 +3112,16 @@
         <v>77</v>
       </c>
       <c r="C71" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D71" t="s">
-        <v>372</v>
+        <v>359</v>
       </c>
       <c r="E71" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F71" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="72" spans="1:6">
@@ -3168,16 +3132,16 @@
         <v>78</v>
       </c>
       <c r="C72" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D72" t="s">
-        <v>373</v>
+        <v>360</v>
       </c>
       <c r="E72" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="F72" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="73" spans="1:6">
@@ -3188,16 +3152,16 @@
         <v>79</v>
       </c>
       <c r="C73" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="D73" t="s">
-        <v>374</v>
+        <v>361</v>
       </c>
       <c r="E73" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="F73" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="74" spans="1:6">
@@ -3208,16 +3172,16 @@
         <v>80</v>
       </c>
       <c r="C74" t="s">
-        <v>229</v>
+        <v>185</v>
       </c>
       <c r="D74" t="s">
-        <v>375</v>
+        <v>362</v>
       </c>
       <c r="E74" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F74" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="75" spans="1:6">
@@ -3228,16 +3192,16 @@
         <v>81</v>
       </c>
       <c r="C75" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D75" t="s">
-        <v>376</v>
+        <v>363</v>
       </c>
       <c r="E75" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="F75" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="76" spans="1:6">
@@ -3248,16 +3212,16 @@
         <v>82</v>
       </c>
       <c r="C76" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D76" t="s">
-        <v>377</v>
+        <v>364</v>
       </c>
       <c r="E76" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="F76" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="77" spans="1:6">
@@ -3268,16 +3232,16 @@
         <v>83</v>
       </c>
       <c r="C77" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D77" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="E77" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F77" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="78" spans="1:6">
@@ -3288,16 +3252,16 @@
         <v>84</v>
       </c>
       <c r="C78" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D78" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="E78" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="F78" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="79" spans="1:6">
@@ -3308,16 +3272,16 @@
         <v>85</v>
       </c>
       <c r="C79" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D79" t="s">
-        <v>380</v>
+        <v>367</v>
       </c>
       <c r="E79" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="F79" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="80" spans="1:6">
@@ -3328,16 +3292,16 @@
         <v>86</v>
       </c>
       <c r="C80" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="D80" t="s">
-        <v>381</v>
+        <v>368</v>
       </c>
       <c r="E80" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="F80" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="81" spans="1:6">
@@ -3348,16 +3312,16 @@
         <v>87</v>
       </c>
       <c r="C81" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D81" t="s">
-        <v>382</v>
+        <v>369</v>
       </c>
       <c r="E81" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="F81" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="82" spans="1:6">
@@ -3368,16 +3332,16 @@
         <v>88</v>
       </c>
       <c r="C82" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D82" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="E82" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F82" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="83" spans="1:6">
@@ -3388,16 +3352,16 @@
         <v>89</v>
       </c>
       <c r="C83" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="D83" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="E83" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F83" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="84" spans="1:6">
@@ -3408,16 +3372,16 @@
         <v>90</v>
       </c>
       <c r="C84" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="D84" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="E84" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="F84" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="85" spans="1:6">
@@ -3428,16 +3392,16 @@
         <v>91</v>
       </c>
       <c r="C85" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D85" t="s">
-        <v>386</v>
+        <v>373</v>
       </c>
       <c r="E85" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F85" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="86" spans="1:6">
@@ -3448,16 +3412,16 @@
         <v>92</v>
       </c>
       <c r="C86" t="s">
-        <v>241</v>
+        <v>171</v>
       </c>
       <c r="D86" t="s">
-        <v>387</v>
+        <v>374</v>
       </c>
       <c r="E86" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="F86" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="87" spans="1:6">
@@ -3468,16 +3432,16 @@
         <v>93</v>
       </c>
       <c r="C87" t="s">
-        <v>242</v>
+        <v>236</v>
       </c>
       <c r="D87" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="E87" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F87" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="88" spans="1:6">
@@ -3488,16 +3452,16 @@
         <v>94</v>
       </c>
       <c r="C88" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D88" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="E88" t="s">
-        <v>457</v>
+        <v>442</v>
       </c>
       <c r="F88" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="89" spans="1:6">
@@ -3508,16 +3472,16 @@
         <v>95</v>
       </c>
       <c r="C89" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="D89" t="s">
-        <v>390</v>
+        <v>377</v>
       </c>
       <c r="E89" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F89" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="90" spans="1:6">
@@ -3528,16 +3492,16 @@
         <v>96</v>
       </c>
       <c r="C90" t="s">
-        <v>214</v>
+        <v>239</v>
       </c>
       <c r="D90" t="s">
-        <v>391</v>
+        <v>378</v>
       </c>
       <c r="E90" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F90" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="91" spans="1:6">
@@ -3548,16 +3512,16 @@
         <v>97</v>
       </c>
       <c r="C91" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="D91" t="s">
-        <v>392</v>
+        <v>379</v>
       </c>
       <c r="E91" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F91" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="92" spans="1:6">
@@ -3568,16 +3532,16 @@
         <v>98</v>
       </c>
       <c r="C92" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="D92" t="s">
-        <v>393</v>
+        <v>380</v>
       </c>
       <c r="E92" t="s">
-        <v>456</v>
+        <v>443</v>
       </c>
       <c r="F92" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="93" spans="1:6">
@@ -3588,16 +3552,16 @@
         <v>99</v>
       </c>
       <c r="C93" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D93" t="s">
-        <v>394</v>
+        <v>381</v>
       </c>
       <c r="E93" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="F93" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="94" spans="1:6">
@@ -3608,16 +3572,16 @@
         <v>100</v>
       </c>
       <c r="C94" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D94" t="s">
-        <v>395</v>
+        <v>382</v>
       </c>
       <c r="E94" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F94" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="95" spans="1:6">
@@ -3628,16 +3592,16 @@
         <v>101</v>
       </c>
       <c r="C95" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="D95" t="s">
-        <v>396</v>
+        <v>383</v>
       </c>
       <c r="E95" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="F95" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="96" spans="1:6">
@@ -3648,16 +3612,16 @@
         <v>102</v>
       </c>
       <c r="C96" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D96" t="s">
-        <v>397</v>
+        <v>384</v>
       </c>
       <c r="E96" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="F96" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="97" spans="1:6">
@@ -3668,16 +3632,16 @@
         <v>103</v>
       </c>
       <c r="C97" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="D97" t="s">
-        <v>398</v>
+        <v>385</v>
       </c>
       <c r="E97" t="s">
-        <v>456</v>
+        <v>444</v>
       </c>
       <c r="F97" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="98" spans="1:6">
@@ -3688,16 +3652,16 @@
         <v>104</v>
       </c>
       <c r="C98" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D98" t="s">
-        <v>399</v>
+        <v>386</v>
       </c>
       <c r="E98" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F98" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="99" spans="1:6">
@@ -3708,16 +3672,16 @@
         <v>105</v>
       </c>
       <c r="C99" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="D99" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
       <c r="E99" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="F99" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="100" spans="1:6">
@@ -3728,16 +3692,16 @@
         <v>106</v>
       </c>
       <c r="C100" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D100" t="s">
-        <v>401</v>
+        <v>388</v>
       </c>
       <c r="E100" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="F100" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="101" spans="1:6">
@@ -3748,16 +3712,16 @@
         <v>107</v>
       </c>
       <c r="C101" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="D101" t="s">
-        <v>402</v>
+        <v>389</v>
       </c>
       <c r="E101" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="F101" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="102" spans="1:6">
@@ -3768,16 +3732,16 @@
         <v>108</v>
       </c>
       <c r="C102" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D102" t="s">
-        <v>403</v>
+        <v>390</v>
       </c>
       <c r="E102" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="F102" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="103" spans="1:6">
@@ -3788,16 +3752,16 @@
         <v>109</v>
       </c>
       <c r="C103" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="D103" t="s">
-        <v>404</v>
+        <v>391</v>
       </c>
       <c r="E103" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="F103" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="104" spans="1:6">
@@ -3808,16 +3772,16 @@
         <v>110</v>
       </c>
       <c r="C104" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D104" t="s">
-        <v>405</v>
+        <v>392</v>
       </c>
       <c r="E104" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F104" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="105" spans="1:6">
@@ -3828,16 +3792,16 @@
         <v>111</v>
       </c>
       <c r="C105" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="D105" t="s">
-        <v>406</v>
+        <v>393</v>
       </c>
       <c r="E105" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="F105" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="106" spans="1:6">
@@ -3848,16 +3812,16 @@
         <v>112</v>
       </c>
       <c r="C106" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D106" t="s">
-        <v>407</v>
+        <v>394</v>
       </c>
       <c r="E106" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F106" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -3868,16 +3832,16 @@
         <v>113</v>
       </c>
       <c r="C107" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D107" t="s">
-        <v>408</v>
+        <v>395</v>
       </c>
       <c r="E107" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="F107" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -3888,16 +3852,16 @@
         <v>114</v>
       </c>
       <c r="C108" t="s">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="D108" t="s">
-        <v>409</v>
+        <v>396</v>
       </c>
       <c r="E108" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="F108" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -3908,16 +3872,16 @@
         <v>115</v>
       </c>
       <c r="C109" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="D109" t="s">
-        <v>410</v>
+        <v>397</v>
       </c>
       <c r="E109" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F109" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -3928,16 +3892,16 @@
         <v>116</v>
       </c>
       <c r="C110" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D110" t="s">
-        <v>411</v>
+        <v>398</v>
       </c>
       <c r="E110" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="F110" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -3948,16 +3912,16 @@
         <v>117</v>
       </c>
       <c r="C111" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="D111" t="s">
-        <v>412</v>
+        <v>399</v>
       </c>
       <c r="E111" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F111" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -3968,19 +3932,19 @@
         <v>118</v>
       </c>
       <c r="C112" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="D112" t="s">
-        <v>413</v>
+        <v>400</v>
       </c>
       <c r="E112" t="s">
-        <v>455</v>
+        <v>441</v>
       </c>
       <c r="F112" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6">
       <c r="A113" t="s">
         <v>7</v>
       </c>
@@ -3988,19 +3952,19 @@
         <v>119</v>
       </c>
       <c r="C113" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="D113" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="E113" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F113" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6">
       <c r="A114" t="s">
         <v>7</v>
       </c>
@@ -4008,19 +3972,19 @@
         <v>120</v>
       </c>
       <c r="C114" t="s">
-        <v>268</v>
+        <v>211</v>
       </c>
       <c r="D114" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="E114" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="F114" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6">
       <c r="A115" t="s">
         <v>7</v>
       </c>
@@ -4028,22 +3992,19 @@
         <v>121</v>
       </c>
       <c r="C115" t="s">
-        <v>269</v>
+        <v>199</v>
       </c>
       <c r="D115" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E115" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="F115" t="s">
-        <v>461</v>
-      </c>
-      <c r="G115" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6">
       <c r="A116" t="s">
         <v>7</v>
       </c>
@@ -4051,19 +4012,19 @@
         <v>122</v>
       </c>
       <c r="C116" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="E116" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="F116" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6">
       <c r="A117" t="s">
         <v>7</v>
       </c>
@@ -4071,19 +4032,19 @@
         <v>123</v>
       </c>
       <c r="C117" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="D117" t="s">
-        <v>418</v>
+        <v>405</v>
       </c>
       <c r="E117" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="F117" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6">
       <c r="A118" t="s">
         <v>7</v>
       </c>
@@ -4091,19 +4052,19 @@
         <v>124</v>
       </c>
       <c r="C118" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="D118" t="s">
-        <v>419</v>
+        <v>406</v>
       </c>
       <c r="E118" t="s">
-        <v>456</v>
+        <v>441</v>
       </c>
       <c r="F118" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6">
       <c r="A119" t="s">
         <v>7</v>
       </c>
@@ -4111,19 +4072,19 @@
         <v>125</v>
       </c>
       <c r="C119" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="D119" t="s">
-        <v>420</v>
+        <v>407</v>
       </c>
       <c r="E119" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="F119" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6">
       <c r="A120" t="s">
         <v>7</v>
       </c>
@@ -4131,19 +4092,19 @@
         <v>126</v>
       </c>
       <c r="C120" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D120" t="s">
-        <v>421</v>
+        <v>408</v>
       </c>
       <c r="E120" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="F120" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6">
       <c r="A121" t="s">
         <v>7</v>
       </c>
@@ -4151,19 +4112,19 @@
         <v>127</v>
       </c>
       <c r="C121" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="D121" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="E121" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F121" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6">
       <c r="A122" t="s">
         <v>7</v>
       </c>
@@ -4171,19 +4132,19 @@
         <v>128</v>
       </c>
       <c r="C122" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="D122" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="E122" t="s">
-        <v>455</v>
+        <v>442</v>
       </c>
       <c r="F122" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6">
       <c r="A123" t="s">
         <v>7</v>
       </c>
@@ -4191,19 +4152,19 @@
         <v>129</v>
       </c>
       <c r="C123" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="D123" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="E123" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="F123" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6">
       <c r="A124" t="s">
         <v>7</v>
       </c>
@@ -4211,19 +4172,19 @@
         <v>130</v>
       </c>
       <c r="C124" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D124" t="s">
-        <v>425</v>
+        <v>412</v>
       </c>
       <c r="E124" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="F124" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6">
       <c r="A125" t="s">
         <v>7</v>
       </c>
@@ -4231,19 +4192,19 @@
         <v>131</v>
       </c>
       <c r="C125" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="D125" t="s">
-        <v>426</v>
+        <v>413</v>
       </c>
       <c r="E125" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="F125" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6">
       <c r="A126" t="s">
         <v>7</v>
       </c>
@@ -4251,19 +4212,19 @@
         <v>132</v>
       </c>
       <c r="C126" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D126" t="s">
-        <v>427</v>
+        <v>414</v>
       </c>
       <c r="E126" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="F126" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6">
       <c r="A127" t="s">
         <v>7</v>
       </c>
@@ -4271,19 +4232,19 @@
         <v>133</v>
       </c>
       <c r="C127" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="D127" t="s">
-        <v>428</v>
+        <v>415</v>
       </c>
       <c r="E127" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="F127" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6">
       <c r="A128" t="s">
         <v>7</v>
       </c>
@@ -4291,16 +4252,16 @@
         <v>134</v>
       </c>
       <c r="C128" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="D128" t="s">
-        <v>429</v>
+        <v>416</v>
       </c>
       <c r="E128" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="F128" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -4311,16 +4272,16 @@
         <v>135</v>
       </c>
       <c r="C129" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="D129" t="s">
-        <v>430</v>
+        <v>417</v>
       </c>
       <c r="E129" t="s">
-        <v>457</v>
+        <v>444</v>
       </c>
       <c r="F129" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -4331,16 +4292,16 @@
         <v>136</v>
       </c>
       <c r="C130" t="s">
-        <v>284</v>
+        <v>197</v>
       </c>
       <c r="D130" t="s">
-        <v>431</v>
+        <v>418</v>
       </c>
       <c r="E130" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="F130" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -4351,16 +4312,16 @@
         <v>137</v>
       </c>
       <c r="C131" t="s">
-        <v>285</v>
+        <v>221</v>
       </c>
       <c r="D131" t="s">
-        <v>432</v>
+        <v>419</v>
       </c>
       <c r="E131" t="s">
-        <v>455</v>
+        <v>440</v>
       </c>
       <c r="F131" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -4371,16 +4332,16 @@
         <v>138</v>
       </c>
       <c r="C132" t="s">
-        <v>221</v>
+        <v>274</v>
       </c>
       <c r="D132" t="s">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="E132" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="F132" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="133" spans="1:6">
@@ -4391,16 +4352,16 @@
         <v>139</v>
       </c>
       <c r="C133" t="s">
-        <v>286</v>
+        <v>200</v>
       </c>
       <c r="D133" t="s">
-        <v>434</v>
+        <v>421</v>
       </c>
       <c r="E133" t="s">
-        <v>454</v>
+        <v>440</v>
       </c>
       <c r="F133" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -4411,16 +4372,16 @@
         <v>140</v>
       </c>
       <c r="C134" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="D134" t="s">
-        <v>435</v>
+        <v>422</v>
       </c>
       <c r="E134" t="s">
-        <v>458</v>
+        <v>445</v>
       </c>
       <c r="F134" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -4431,16 +4392,16 @@
         <v>141</v>
       </c>
       <c r="C135" t="s">
-        <v>288</v>
+        <v>192</v>
       </c>
       <c r="D135" t="s">
-        <v>436</v>
+        <v>423</v>
       </c>
       <c r="E135" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F135" t="s">
-        <v>459</v>
+        <v>447</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -4451,16 +4412,16 @@
         <v>142</v>
       </c>
       <c r="C136" t="s">
-        <v>289</v>
+        <v>276</v>
       </c>
       <c r="D136" t="s">
-        <v>437</v>
+        <v>424</v>
       </c>
       <c r="E136" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F136" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -4471,16 +4432,16 @@
         <v>143</v>
       </c>
       <c r="C137" t="s">
-        <v>290</v>
+        <v>277</v>
       </c>
       <c r="D137" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="E137" t="s">
-        <v>454</v>
+        <v>442</v>
       </c>
       <c r="F137" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -4491,16 +4452,16 @@
         <v>144</v>
       </c>
       <c r="C138" t="s">
-        <v>291</v>
+        <v>278</v>
       </c>
       <c r="D138" t="s">
-        <v>439</v>
+        <v>426</v>
       </c>
       <c r="E138" t="s">
-        <v>457</v>
+        <v>445</v>
       </c>
       <c r="F138" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -4511,16 +4472,16 @@
         <v>145</v>
       </c>
       <c r="C139" t="s">
-        <v>228</v>
+        <v>196</v>
       </c>
       <c r="D139" t="s">
-        <v>440</v>
+        <v>427</v>
       </c>
       <c r="E139" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F139" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -4531,16 +4492,16 @@
         <v>146</v>
       </c>
       <c r="C140" t="s">
-        <v>292</v>
+        <v>169</v>
       </c>
       <c r="D140" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="E140" t="s">
-        <v>458</v>
+        <v>443</v>
       </c>
       <c r="F140" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -4551,16 +4512,16 @@
         <v>147</v>
       </c>
       <c r="C141" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="D141" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="E141" t="s">
-        <v>457</v>
+        <v>440</v>
       </c>
       <c r="F141" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -4571,16 +4532,16 @@
         <v>148</v>
       </c>
       <c r="C142" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="D142" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="E142" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F142" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -4591,16 +4552,16 @@
         <v>149</v>
       </c>
       <c r="C143" t="s">
-        <v>167</v>
+        <v>281</v>
       </c>
       <c r="D143" t="s">
+        <v>431</v>
+      </c>
+      <c r="E143" t="s">
         <v>444</v>
       </c>
-      <c r="E143" t="s">
-        <v>458</v>
-      </c>
       <c r="F143" t="s">
-        <v>461</v>
+        <v>448</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -4611,16 +4572,16 @@
         <v>150</v>
       </c>
       <c r="C144" t="s">
-        <v>295</v>
+        <v>282</v>
       </c>
       <c r="D144" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="E144" t="s">
-        <v>453</v>
+        <v>440</v>
       </c>
       <c r="F144" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -4631,16 +4592,16 @@
         <v>151</v>
       </c>
       <c r="C145" t="s">
-        <v>296</v>
+        <v>283</v>
       </c>
       <c r="D145" t="s">
-        <v>446</v>
+        <v>433</v>
       </c>
       <c r="E145" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
       <c r="F145" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -4651,16 +4612,16 @@
         <v>152</v>
       </c>
       <c r="C146" t="s">
-        <v>297</v>
+        <v>284</v>
       </c>
       <c r="D146" t="s">
-        <v>447</v>
+        <v>434</v>
       </c>
       <c r="E146" t="s">
-        <v>455</v>
+        <v>443</v>
       </c>
       <c r="F146" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -4671,16 +4632,16 @@
         <v>153</v>
       </c>
       <c r="C147" t="s">
-        <v>298</v>
+        <v>285</v>
       </c>
       <c r="D147" t="s">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="E147" t="s">
-        <v>457</v>
+        <v>441</v>
       </c>
       <c r="F147" t="s">
-        <v>460</v>
+        <v>447</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -4691,16 +4652,16 @@
         <v>154</v>
       </c>
       <c r="C148" t="s">
-        <v>299</v>
+        <v>286</v>
       </c>
       <c r="D148" t="s">
-        <v>449</v>
+        <v>436</v>
       </c>
       <c r="E148" t="s">
-        <v>458</v>
+        <v>444</v>
       </c>
       <c r="F148" t="s">
-        <v>459</v>
+        <v>446</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -4711,16 +4672,16 @@
         <v>155</v>
       </c>
       <c r="C149" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="D149" t="s">
-        <v>450</v>
+        <v>437</v>
       </c>
       <c r="E149" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F149" t="s">
-        <v>460</v>
+        <v>448</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -4731,16 +4692,16 @@
         <v>156</v>
       </c>
       <c r="C150" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="D150" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="E150" t="s">
-        <v>454</v>
+        <v>441</v>
       </c>
       <c r="F150" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -4751,16 +4712,16 @@
         <v>157</v>
       </c>
       <c r="C151" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="D151" t="s">
-        <v>452</v>
+        <v>439</v>
       </c>
       <c r="E151" t="s">
-        <v>458</v>
+        <v>440</v>
       </c>
       <c r="F151" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
     </row>
   </sheetData>
